--- a/second-thought/data/source/cognitive_bias_trainer.xlsx
+++ b/second-thought/data/source/cognitive_bias_trainer.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="11" min="1" max="1"/>
@@ -701,6 +701,21 @@
           <t>Tier</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Usually Confused With</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Noticing Cue</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Further Reading URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1" s="12">
       <c r="A2" s="19" t="inlineStr">
@@ -741,6 +756,21 @@
       <c r="H2" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Belief Perseverance, Choice-Supportive Bias</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Am I mostly collecting evidence that already agrees with me?</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Confirmation_bias</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="60" customHeight="1" s="12">
       <c r="A3" s="19" t="inlineStr">
@@ -781,6 +811,21 @@
       <c r="H3" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Framing Effect</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Would I pick the same number if I had never seen the first figure?</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Anchoring_(cognitive_bias)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1" s="12">
       <c r="A4" s="19" t="inlineStr">
@@ -821,6 +866,21 @@
       <c r="H4" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Recency Bias, Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Is this easy to recall — or actually common?</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Availability_heuristic</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1" s="12">
       <c r="A5" s="19" t="inlineStr">
@@ -861,6 +921,21 @@
       <c r="H5" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Actor-Observer Bias, Hostile Attribution Bias</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Would I give myself the same excuse if I were in their situation?</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fundamental_attribution_error</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="12">
       <c r="A6" s="19" t="inlineStr">
@@ -901,6 +976,21 @@
       <c r="H6" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Actor-Observer Bias, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Am I claiming the wins and blaming the situation for the losses?</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Self-serving_bias</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="12">
       <c r="A7" s="19" t="inlineStr">
@@ -941,6 +1031,21 @@
       <c r="H7" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Loss Aversion, Status Quo Bias, Endowment Effect</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>If I were deciding for the first time today, would I still continue?</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sunk_cost#Loss_aversion_and_the_sunk_cost_fallacy</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="12">
       <c r="A8" s="19" t="inlineStr">
@@ -981,6 +1086,21 @@
       <c r="H8" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Loss Aversion</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Am I weighting one bad moment more heavily than equally strong good ones?</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Negativity_bias</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="12">
       <c r="A9" s="19" t="inlineStr">
@@ -1021,6 +1141,21 @@
       <c r="H9" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Horn Effect, Authority Bias</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Am I rating other traits higher just because I already like this person?</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Halo_effect</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="12">
       <c r="A10" s="19" t="inlineStr">
@@ -1061,6 +1196,21 @@
       <c r="H10" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Halo Effect</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Am I assuming more negatives because of one bad impression?</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Horn_effect</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="12">
       <c r="A11" s="19" t="inlineStr">
@@ -1101,6 +1251,21 @@
       <c r="H11" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Whose stories am I missing because they did not “make it”?</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Survivorship_bias</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="60" customHeight="1" s="12">
       <c r="A12" s="19" t="inlineStr">
@@ -1141,6 +1306,21 @@
       <c r="H12" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Did I predict this beforehand — or does it only feel obvious now?</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hindsight_bias</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="60" customHeight="1" s="12">
       <c r="A13" s="19" t="inlineStr">
@@ -1181,6 +1361,21 @@
       <c r="H13" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>In-group Bias, Naive Realism</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Have I checked whether people outside my circle actually agree?</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/False_consensus_effect</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1" s="12">
       <c r="A14" s="19" t="inlineStr">
@@ -1221,6 +1416,21 @@
       <c r="H14" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Out-group Homogeneity Bias, False Consensus Effect</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Would I judge this the same way if they were outside my group?</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/In-group_favoritism</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="12">
       <c r="A15" s="19" t="inlineStr">
@@ -1261,6 +1471,21 @@
       <c r="H15" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>In-group Bias, Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Am I treating “them” as all alike while seeing variety in my own group?</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Out-group_homogeneity</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="12">
       <c r="A16" s="19" t="inlineStr">
@@ -1301,6 +1526,21 @@
       <c r="H16" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Anchoring Bias, Loss Aversion</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Would my choice change if the same facts were worded differently?</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Framing_effect_(psychology)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1" s="12">
       <c r="A17" s="19" t="inlineStr">
@@ -1341,6 +1581,21 @@
       <c r="H17" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sunk Cost Fallacy, Endowment Effect, Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Am I avoiding a loss harder than I would chase an equal gain?</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Loss_aversion</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1" s="12">
       <c r="A18" s="19" t="inlineStr">
@@ -1381,6 +1636,21 @@
       <c r="H18" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect, Planning Fallacy, Illusion of Control</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>What would a realistic base rate say about my odds?</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Optimism_bias</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="60" customHeight="1" s="12">
       <c r="A19" s="19" t="inlineStr">
@@ -1421,6 +1691,21 @@
       <c r="H19" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sunk Cost Fallacy, Endowment Effect, Normalcy Bias</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Am I keeping this because it is better — or just because it is current?</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Status_quo_bias</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1" s="12">
       <c r="A20" s="19" t="inlineStr">
@@ -1461,6 +1746,21 @@
       <c r="H20" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Have I tested my confidence against feedback from someone more experienced?</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dunning%E2%80%93Kruger_effect</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="60" customHeight="1" s="12">
       <c r="A21" s="19" t="inlineStr">
@@ -1500,6 +1800,21 @@
       </c>
       <c r="H21" s="11" t="n">
         <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Halo Effect, Bandwagon Effect</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Am I trusting this because of the title — or because of the reasons?</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Authority_bias</t>
+        </is>
       </c>
     </row>
     <row r="22">

--- a/second-thought/data/source/cognitive_bias_trainer.xlsx
+++ b/second-thought/data/source/cognitive_bias_trainer.xlsx
@@ -701,17 +701,17 @@
           <t>Tier</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Usually Confused With</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Noticing Cue</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>In clearer terms</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Further Reading URL</t>
         </is>
@@ -756,17 +756,17 @@
       <c r="H2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>Belief Perseverance, Choice-Supportive Bias</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Am I mostly collecting evidence that already agrees with me?</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to seek, interpret, favour, and remember information that supports what we already believe, while giving less weight to information that challenges it.</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Confirmation_bias</t>
         </is>
@@ -811,17 +811,17 @@
       <c r="H3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>Framing Effect</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Would I pick the same number if I had never seen the first figure?</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to rely too heavily on an initial piece of information (an “anchor”) when making estimates or decisions, even when that starting point is arbitrary.</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Anchoring_(cognitive_bias)</t>
         </is>
@@ -866,17 +866,17 @@
       <c r="H4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>Recency Bias, Representativeness Heuristic</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Is this easy to recall — or actually common?</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>A mental shortcut where we judge how common or likely something is by how easily examples come to mind, which can make vivid or recent events feel more frequent than they are.</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Availability_heuristic</t>
         </is>
@@ -921,17 +921,17 @@
       <c r="H5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>Actor-Observer Bias, Hostile Attribution Bias</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Would I give myself the same excuse if I were in their situation?</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to explain other people’s actions mainly by their character or personality, while underestimating the role of the situation they are in.</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Fundamental_attribution_error</t>
         </is>
@@ -976,17 +976,17 @@
       <c r="H6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Actor-Observer Bias, Egocentric Bias</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Am I claiming the wins and blaming the situation for the losses?</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to credit our successes to our own ability or effort, and to blame our failures on outside circumstances, bad luck, or other people.</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Self-serving_bias</t>
         </is>
@@ -1031,17 +1031,17 @@
       <c r="H7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>Loss Aversion, Status Quo Bias, Endowment Effect</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>If I were deciding for the first time today, would I still continue?</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to continue with a plan or investment because of what we have already put in (time, money, or effort), rather than because future benefits still justify it.</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Sunk_cost#Loss_aversion_and_the_sunk_cost_fallacy</t>
         </is>
@@ -1086,17 +1086,17 @@
       <c r="H8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>Loss Aversion</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Am I weighting one bad moment more heavily than equally strong good ones?</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>The tendency for negative events, information, or emotions to affect us more strongly than positive ones of equal intensity.</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Negativity_bias</t>
         </is>
@@ -1141,17 +1141,17 @@
       <c r="H9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>Horn Effect, Authority Bias</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Am I rating other traits higher just because I already like this person?</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>When a positive overall impression of someone (or something) spills over and makes us rate their other traits more favourably than the evidence supports.</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Halo_effect</t>
         </is>
@@ -1196,17 +1196,17 @@
       <c r="H10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Halo Effect</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Am I assuming more negatives because of one bad impression?</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>When a negative overall impression of someone (or something) spills over and makes us rate their other traits more harshly than the evidence supports.</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Horn_effect</t>
         </is>
@@ -1251,17 +1251,17 @@
       <c r="H11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>Availability Heuristic</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Whose stories am I missing because they did not “make it”?</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible — which can distort what we think works.</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Survivorship_bias</t>
         </is>
@@ -1306,17 +1306,17 @@
       <c r="H12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Did I predict this beforehand — or does it only feel obvious now?</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>The tendency, after an outcome is known, to see it as more predictable than it really was, and to believe we “knew it all along.”</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Hindsight_bias</t>
         </is>
@@ -1361,17 +1361,17 @@
       <c r="H13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>In-group Bias, Naive Realism</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Have I checked whether people outside my circle actually agree?</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how widely others share our beliefs, preferences, and behaviours.</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/False_consensus_effect</t>
         </is>
@@ -1416,17 +1416,17 @@
       <c r="H14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>Out-group Homogeneity Bias, False Consensus Effect</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Would I judge this the same way if they were outside my group?</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to favour people who belong to our own group — giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/In-group_favoritism</t>
         </is>
@@ -1471,17 +1471,17 @@
       <c r="H15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>In-group Bias, Representativeness Heuristic</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Am I treating “them” as all alike while seeing variety in my own group?</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to see people in other groups as more alike than they are, while seeing members of our own group as more varied and individual.</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Out-group_homogeneity</t>
         </is>
@@ -1526,17 +1526,17 @@
       <c r="H16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>Anchoring Bias, Loss Aversion</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Would my choice change if the same facts were worded differently?</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented — for example as gains versus losses.</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Framing_effect_(psychology)</t>
         </is>
@@ -1581,17 +1581,17 @@
       <c r="H17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>Sunk Cost Fallacy, Endowment Effect, Negativity Bias</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Am I avoiding a loss harder than I would chase an equal gain?</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>The tendency for losses to feel more painful than gains of the same size feel rewarding, which can make us overly cautious about potential losses.</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Loss_aversion</t>
         </is>
@@ -1636,17 +1636,17 @@
       <c r="H18" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect, Planning Fallacy, Illusion of Control</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>What would a realistic base rate say about my odds?</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how likely good things are to happen to us, and to underestimate our personal risk of bad outcomes compared with other people.</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Optimism_bias</t>
         </is>
@@ -1691,17 +1691,17 @@
       <c r="H19" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>Sunk Cost Fallacy, Endowment Effect, Normalcy Bias</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Am I keeping this because it is better — or just because it is current?</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to prefer the current state of affairs and to treat “keeping things as they are” as the default choice, even when change might be better.</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Status_quo_bias</t>
         </is>
@@ -1746,17 +1746,17 @@
       <c r="H20" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Have I tested my confidence against feedback from someone more experienced?</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>A pattern where people with limited skill or knowledge in an area overestimate how competent they are, partly because the same gaps that cause mistakes also hide those mistakes from view.</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Dunning%E2%80%93Kruger_effect</t>
         </is>
@@ -1801,17 +1801,17 @@
       <c r="H21" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>Halo Effect, Bandwagon Effect</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Am I trusting this because of the title — or because of the reasons?</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to trust or follow the views of someone seen as an authority more than the strength of their arguments alone would justify.</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Authority_bias</t>
         </is>

--- a/second-thought/data/source/cognitive_bias_trainer.xlsx
+++ b/second-thought/data/source/cognitive_bias_trainer.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="11" min="1" max="1"/>
@@ -708,11 +708,6 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>In clearer terms</t>
-        </is>
-      </c>
-      <c r="K1" s="11" t="inlineStr">
-        <is>
           <t>Further Reading URL</t>
         </is>
       </c>
@@ -730,7 +725,7 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>We tend to search for, interpret, and recall information that confirms our existing beliefs.</t>
+          <t>The tendency to seek, interpret, favour, and remember information that supports what we already believe, while giving less weight to information that challenges it.</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
@@ -763,11 +758,6 @@
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>The tendency to seek, interpret, favour, and remember information that supports what we already believe, while giving less weight to information that challenges it.</t>
-        </is>
-      </c>
-      <c r="K2" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Confirmation_bias</t>
         </is>
       </c>
@@ -785,7 +775,7 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>We rely too heavily on the first piece of information offered (the 'anchor') when making decisions.</t>
+          <t>The tendency to rely too heavily on an initial piece of information (an “anchor”) when making estimates or decisions, even when that starting point is arbitrary.</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
@@ -818,11 +808,6 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>The tendency to rely too heavily on an initial piece of information (an “anchor”) when making estimates or decisions, even when that starting point is arbitrary.</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Anchoring_(cognitive_bias)</t>
         </is>
       </c>
@@ -840,7 +825,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>We judge the likelihood of events based on how easily examples come to mind.</t>
+          <t>A mental shortcut where we judge how common or likely something is by how easily examples come to mind, which can make vivid or recent events feel more frequent than they are.</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
@@ -873,11 +858,6 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>A mental shortcut where we judge how common or likely something is by how easily examples come to mind, which can make vivid or recent events feel more frequent than they are.</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Availability_heuristic</t>
         </is>
       </c>
@@ -895,7 +875,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>We judge others' behavior as caused by their character, while excusing our own behavior as caused by circumstances.</t>
+          <t>The tendency to explain other people’s actions mainly by their character or personality, while underestimating the role of the situation they are in.</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -928,11 +908,6 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>The tendency to explain other people’s actions mainly by their character or personality, while underestimating the role of the situation they are in.</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Fundamental_attribution_error</t>
         </is>
       </c>
@@ -950,7 +925,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>We attribute our successes to our own abilities and our failures to external circumstances.</t>
+          <t>The tendency to credit our successes to our own ability or effort, and to blame our failures on outside circumstances, bad luck, or other people.</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
@@ -983,11 +958,6 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>The tendency to credit our successes to our own ability or effort, and to blame our failures on outside circumstances, bad luck, or other people.</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Self-serving_bias</t>
         </is>
       </c>
@@ -1005,7 +975,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>We continue investing in something because of what we've already invested, rather than evaluating future value.</t>
+          <t>The tendency to continue with a plan or investment because of what we have already put in (time, money, or effort), rather than because future benefits still justify it.</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -1038,11 +1008,6 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>The tendency to continue with a plan or investment because of what we have already put in (time, money, or effort), rather than because future benefits still justify it.</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Sunk_cost#Loss_aversion_and_the_sunk_cost_fallacy</t>
         </is>
       </c>
@@ -1060,7 +1025,7 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>We give more psychological weight to negative experiences than to positive ones of equal intensity.</t>
+          <t>The tendency for negative events, information, or emotions to affect us more strongly than positive ones of equal intensity.</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -1093,11 +1058,6 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>The tendency for negative events, information, or emotions to affect us more strongly than positive ones of equal intensity.</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Negativity_bias</t>
         </is>
       </c>
@@ -1115,7 +1075,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Our overall impression of a person influences how we judge their specific traits, so one positive trait makes us assume other positive traits.</t>
+          <t>When a positive overall impression of someone (or something) spills over and makes us rate their other traits more favourably than the evidence supports.</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -1148,11 +1108,6 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>When a positive overall impression of someone (or something) spills over and makes us rate their other traits more favourably than the evidence supports.</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Halo_effect</t>
         </is>
       </c>
@@ -1170,7 +1125,7 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>One negative trait about a person leads us to assume other negative traits, the opposite of the halo effect.</t>
+          <t>When a negative overall impression of someone (or something) spills over and makes us rate their other traits more harshly than the evidence supports.</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -1203,11 +1158,6 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>When a negative overall impression of someone (or something) spills over and makes us rate their other traits more harshly than the evidence supports.</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Horn_effect</t>
         </is>
       </c>
@@ -1225,7 +1175,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>We focus on the people or things that 'survived' a process, while overlooking those that didn't, skewing our conclusions.</t>
+          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible — which can distort what we think works.</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -1258,11 +1208,6 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible — which can distort what we think works.</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Survivorship_bias</t>
         </is>
       </c>
@@ -1280,7 +1225,7 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>After an event happens, we tend to believe we 'knew it all along,' even if we couldn't have predicted it beforehand.</t>
+          <t>The tendency, after an outcome is known, to see it as more predictable than it really was, and to believe we “knew it all along.”</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -1313,11 +1258,6 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>The tendency, after an outcome is known, to see it as more predictable than it really was, and to believe we “knew it all along.”</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Hindsight_bias</t>
         </is>
       </c>
@@ -1335,7 +1275,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>We overestimate how much other people share our beliefs, opinions, and behaviors.</t>
+          <t>The tendency to overestimate how widely others share our beliefs, preferences, and behaviours.</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -1368,11 +1308,6 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>The tendency to overestimate how widely others share our beliefs, preferences, and behaviours.</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/False_consensus_effect</t>
         </is>
       </c>
@@ -1390,7 +1325,7 @@
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>We favor members of our own group over members of other groups, often unconsciously.</t>
+          <t>The tendency to favour people who belong to our own group — giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1423,11 +1358,6 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>The tendency to favour people who belong to our own group — giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/In-group_favoritism</t>
         </is>
       </c>
@@ -1445,7 +1375,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>We tend to see members of other groups as more similar to each other than they really are, while seeing our own group as diverse.</t>
+          <t>The tendency to see people in other groups as more alike than they are, while seeing members of our own group as more varied and individual.</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -1478,11 +1408,6 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>The tendency to see people in other groups as more alike than they are, while seeing members of our own group as more varied and individual.</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Out-group_homogeneity</t>
         </is>
       </c>
@@ -1500,7 +1425,7 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>Our decisions are influenced by how information is presented (framed), even when the underlying facts are the same.</t>
+          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented — for example as gains versus losses.</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -1533,11 +1458,6 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented — for example as gains versus losses.</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Framing_effect_(psychology)</t>
         </is>
       </c>
@@ -1555,7 +1475,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>The pain of losing something feels psychologically stronger than the pleasure of gaining something of equal value.</t>
+          <t>The tendency for losses to feel more painful than gains of the same size feel rewarding, which can make us overly cautious about potential losses.</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1588,11 +1508,6 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>The tendency for losses to feel more painful than gains of the same size feel rewarding, which can make us overly cautious about potential losses.</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Loss_aversion</t>
         </is>
       </c>
@@ -1610,7 +1525,7 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>We tend to overestimate the likelihood of positive events happening to us and underestimate the likelihood of negative ones.</t>
+          <t>The tendency to overestimate how likely good things are to happen to us, and to underestimate our personal risk of bad outcomes compared with other people.</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -1643,11 +1558,6 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>The tendency to overestimate how likely good things are to happen to us, and to underestimate our personal risk of bad outcomes compared with other people.</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Optimism_bias</t>
         </is>
       </c>
@@ -1665,7 +1575,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>We prefer things to stay the same, and treat the current state as a reasonable default, even when change might be better.</t>
+          <t>The tendency to prefer the current state of affairs and to treat “keeping things as they are” as the default choice, even when change might be better.</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1698,11 +1608,6 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>The tendency to prefer the current state of affairs and to treat “keeping things as they are” as the default choice, even when change might be better.</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Status_quo_bias</t>
         </is>
       </c>
@@ -1720,7 +1625,7 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>People with limited knowledge or skill in an area tend to overestimate their own competence.</t>
+          <t>A pattern where people with limited skill or knowledge in an area overestimate how competent they are, partly because the same gaps that cause mistakes also hide those mistakes from view.</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -1753,11 +1658,6 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>A pattern where people with limited skill or knowledge in an area overestimate how competent they are, partly because the same gaps that cause mistakes also hide those mistakes from view.</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Dunning%E2%80%93Kruger_effect</t>
         </is>
       </c>
@@ -1775,7 +1675,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>We tend to attribute greater accuracy and trust to the opinions of an authority figure, regardless of the actual content.</t>
+          <t>The tendency to trust or follow the views of someone seen as an authority more than the strength of their arguments alone would justify.</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -1808,11 +1708,6 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>The tendency to trust or follow the views of someone seen as an authority more than the strength of their arguments alone would justify.</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
           <t>https://en.wikipedia.org/wiki/Authority_bias</t>
         </is>
       </c>
@@ -1830,7 +1725,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>We routinely underestimate how long tasks will take and overestimate how smoothly they will go.</t>
+          <t>The tendency to underestimate how long a task will take and how many obstacles will appear, even when similar tasks have overrun before.</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1856,6 +1751,16 @@
       <c r="H22" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Planning_fallacy</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -1870,7 +1775,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>We give more weight to recent events than to older ones, even when the older pattern matters more.</t>
+          <t>The tendency to give recent information more weight than older information, even when the longer track record is more informative.</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1896,6 +1801,16 @@
       <c r="H23" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Recency_bias</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -1910,7 +1825,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>We are more likely to adopt a belief or behaviour because many others are doing it.</t>
+          <t>The tendency to adopt a belief or behaviour because many other people are doing so, treating popularity as a signal that it must be right.</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1936,6 +1851,16 @@
       <c r="H24" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Authority Bias, In-group Bias</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bandwagon_effect</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -1950,7 +1875,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>We tend to like things more simply because we have encountered them before.</t>
+          <t>The tendency to like people, ideas, or things more simply because we have encountered them before, even without stronger reasons to prefer them.</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1976,6 +1901,16 @@
       <c r="H25" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Status Quo Bias, Illusory Truth Effect</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mere-exposure_effect</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -1990,7 +1925,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>We value things more highly simply because we already own them.</t>
+          <t>The tendency to value something more highly once we own it than we would if the same item belonged to someone else.</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -2016,6 +1951,16 @@
       <c r="H26" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Loss Aversion, Status Quo Bias, Sunk Cost Fallacy</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Endowment_effect</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -2030,7 +1975,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>We expect random events to balance out in the short run, as if past outcomes change future odds.</t>
+          <t>The belief that a random event is “due” after a streak of opposite outcomes, as if chance keeps a short-run balance sheet.</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -2056,6 +2001,16 @@
       <c r="H27" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Clustering Illusion, Illusion of Control</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gambler%27s_fallacy</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -2070,7 +2025,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>We see meaningful patterns in small sets of random or unrelated events.</t>
+          <t>The tendency to see meaningful patterns or streaks in small samples of random or unrelated events.</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -2096,6 +2051,16 @@
       <c r="H28" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Gambler's Fallacy, Illusory Correlation</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Clustering_illusion</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -2110,7 +2075,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>We judge how likely something is by how much it resembles a stereotype, instead of using actual odds.</t>
+          <t>A mental shortcut where we judge probability by how much something resembles a familiar stereotype or story, instead of using actual base rates.</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -2136,6 +2101,16 @@
       <c r="H29" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Base Rate Neglect, Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Representativeness_heuristic</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -2150,7 +2125,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>We ignore general base-rate information and focus on specific, vivid details instead.</t>
+          <t>The tendency to ignore general statistical information about how common something is, and to focus instead on specific, vivid details.</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -2176,6 +2151,16 @@
       <c r="H30" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Representativeness Heuristic, Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Base_rate_fallacy</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -2190,7 +2175,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>We judge an experience mainly by its most intense moment and how it ended, not the whole duration.</t>
+          <t>The tendency to judge an experience mainly by its most intense moment and how it ended, rather than by the whole duration.</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -2216,6 +2201,16 @@
       <c r="H31" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Peak%E2%80%93end_rule</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -2230,7 +2225,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>After making a choice, we remember the chosen option more favourably and downplay its downsides.</t>
+          <t>The tendency, after we have chosen an option, to remember it more favourably and to downplay its downsides or the appeal of alternatives.</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -2256,6 +2251,16 @@
       <c r="H32" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Confirmation Bias, Cognitive Dissonance</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Choice-supportive_bias</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -2270,7 +2275,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>We overestimate how much influence we have over outcomes that are mostly chance or outside our control.</t>
+          <t>The tendency to overestimate how much influence our actions have over outcomes that are largely random or outside our control.</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -2296,6 +2301,16 @@
       <c r="H33" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Gambler's Fallacy</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusion_of_control</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -2310,7 +2325,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>We overestimate how much other people notice our appearance, mistakes, or behaviour.</t>
+          <t>The tendency to overestimate how much other people notice our appearance, mistakes, or behaviour.</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -2336,6 +2351,16 @@
       <c r="H34" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Illusion of Transparency, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Spotlight_effect</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -2350,7 +2375,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>When our actions clash with our beliefs, we often change our beliefs or excuses rather than face the clash.</t>
+          <t>The mental discomfort that arises when our actions conflict with our beliefs, often leading us to justify, minimise, or reframe what we did.</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -2376,6 +2401,16 @@
       <c r="H35" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Choice-Supportive Bias, Belief Perseverance</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cognitive_dissonance</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -2390,7 +2425,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>We keep believing something even after the evidence supporting it has been weakened or removed.</t>
+          <t>The tendency to hold on to a belief even after the evidence that supported it has been weakened or removed.</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -2416,6 +2451,16 @@
       <c r="H36" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Confirmation Bias, Semmelweis Reflex</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Belief_perseverance</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -2430,7 +2475,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>We underestimate the chance of disruption and assume things will keep going as they usually do.</t>
+          <t>The tendency to underestimate the likelihood of serious disruption and to assume that life will continue in the usual way.</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2456,6 +2501,16 @@
       <c r="H37" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Status Quo Bias, Optimism Bias</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Normalcy_bias</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -2470,7 +2525,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Once we know something, we find it hard to imagine not knowing it.</t>
+          <t>The difficulty of remembering what it was like not to know something, which can make experts skip steps that beginners still need.</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2496,6 +2551,16 @@
       <c r="H38" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>False Consensus Effect, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Curse_of_knowledge</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -2510,7 +2575,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>We perceive a link between two things when none exists, or see a stronger link than the data supports.</t>
+          <t>The tendency to perceive a relationship between two things when none exists, or to see a stronger link than the evidence supports.</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -2536,6 +2601,16 @@
       <c r="H39" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Clustering Illusion, Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusory_correlation</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -2550,7 +2625,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>We judge a detailed, specific story as more likely than a broader, more general one.</t>
+          <t>The tendency to judge a detailed, specific scenario as more probable than a broader one, even though added detail usually makes an event less likely.</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -2576,6 +2651,16 @@
       <c r="H40" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Conjunction_fallacy</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -2590,7 +2675,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Repeated statements feel more true, even when we know we should check them.</t>
+          <t>The tendency for repeated statements to feel more true, simply because they have become familiar.</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -2616,6 +2701,16 @@
       <c r="H41" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Mere Exposure Effect, Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusory_truth_effect</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -2630,7 +2725,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>We explain other people's actions by their character, but our own by the situation.</t>
+          <t>The tendency to explain other people’s behaviour by their character, while explaining our own behaviour by the situation we were in.</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -2656,6 +2751,16 @@
       <c r="H42" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error, Self-serving Bias</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Actor%E2%80%93observer_asymmetry</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -2670,7 +2775,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>We notice biases in others more easily than in ourselves.</t>
+          <t>The tendency to recognise cognitive biases more easily in other people than in ourselves.</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -2696,6 +2801,16 @@
       <c r="H43" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Naive Realism, Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bias_blind_spot</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -2710,7 +2825,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>We believe we see reality directly and that reasonable people should agree with us.</t>
+          <t>The belief that we see the world objectively, and that people who disagree with us must be uninformed, irrational, or biased.</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -2736,6 +2851,16 @@
       <c r="H44" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>False Consensus Effect, Bias Blind Spot</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Na%C3%AFve_realism_(psychology)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -2750,7 +2875,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>We assume people generally get what they deserve, and search for reasons bad outcomes were earned.</t>
+          <t>The tendency to assume the world is fair and that people usually get what they deserve, which can lead us to blame victims or downplay luck.</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -2776,6 +2901,16 @@
       <c r="H45" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error, Hindsight Bias</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Just-world_hypothesis</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2790,7 +2925,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>We interpret ambiguous actions from others as intentionally hostile or unkind.</t>
+          <t>The tendency to interpret ambiguous actions from others as intentionally hostile, unkind, or personally directed.</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -2816,6 +2951,16 @@
       <c r="H46" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error, Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hostile_attribution_bias</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -2830,7 +2975,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>We remember our own role in events as larger and more central than it was.</t>
+          <t>The tendency to remember our own role, effort, or importance in joint events as larger than it really was.</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -2856,6 +3001,16 @@
       <c r="H47" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Self-serving Bias, Spotlight Effect</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Egocentric_bias</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -2870,7 +3025,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>We overestimate how clearly others can read our emotions and thoughts.</t>
+          <t>The tendency to overestimate how easily other people can read our emotions, thoughts, or internal state.</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2896,6 +3051,16 @@
       <c r="H48" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Spotlight Effect, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusion_of_transparency</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -2910,7 +3075,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>We prefer smaller rewards now over larger rewards later, more steeply than calm planning would suggest.</t>
+          <t>The tendency to prefer smaller rewards now over larger rewards later, more steeply than a calm long-term plan would suggest.</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -2936,6 +3101,16 @@
       <c r="H49" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Restraint Bias</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hyperbolic_discounting</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -2950,7 +3125,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>We avoid options when the odds of a good outcome are unclear, even if they might be favourable.</t>
+          <t>The tendency to avoid options when the probability of a good outcome is unclear, even if those options could be better than a known alternative.</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -2976,6 +3151,16 @@
       <c r="H50" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Status Quo Bias, Loss Aversion</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ambiguity_effect</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -2990,7 +3175,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>We respond more strongly to one identifiable person in need than to large, statistical groups.</t>
+          <t>The tendency to feel and give more help in response to one identifiable person in need than to large groups described only with statistics.</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -3016,6 +3201,16 @@
       <c r="H51" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Availability Heuristic, Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Identifiable_victim_effect</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -3030,7 +3225,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>We overestimate our ability to resist temptation in the moment.</t>
+          <t>The tendency to overestimate how well we will resist temptation when the moment actually arrives.</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -3056,6 +3251,16 @@
       <c r="H52" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect, Optimism Bias</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Restraint_bias</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -3070,7 +3275,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>When we feel our freedom is threatened, we push back — sometimes by doing the opposite.</t>
+          <t>The tendency to push back when we feel our freedom is being restricted — sometimes by doing the opposite of what we are urged to do.</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -3096,6 +3301,16 @@
       <c r="H53" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Status Quo Bias</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Reactance_(psychology)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -3110,7 +3325,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>We avoid information that might force us to face an uncomfortable problem.</t>
+          <t>The tendency to avoid looking at information that might confirm a problem we would rather not face.</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -3136,6 +3351,16 @@
       <c r="H54" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Normalcy Bias</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ostrich_effect</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -3150,7 +3375,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>We treat situations as if one person's gain must mean another person's loss, even when both could benefit.</t>
+          <t>The tendency to treat a situation as if one person’s gain must mean another person’s loss, even when both could benefit.</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -3176,6 +3401,16 @@
       <c r="H55" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>In-group Bias</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Zero-sum_thinking</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -3190,7 +3425,7 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>We judge the morality of an action partly by how lucky or unlucky the outcome was.</t>
+          <t>The tendency to judge how good or bad a decision was partly by how lucky or unlucky the outcome turned out to be.</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -3216,6 +3451,16 @@
       <c r="H56" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Hindsight Bias, Fundamental Attribution Error</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Moral_luck</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -3230,7 +3475,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>We notice a cluster first, then draw a target around it as if we predicted it.</t>
+          <t>The tendency to notice a cluster in data first, then treat that cluster as if it had been predicted — drawing the target after the shots.</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -3256,6 +3501,16 @@
       <c r="H57" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Clustering Illusion, Illusory Correlation</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Texas_sharpshooter_fallacy</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -3270,7 +3525,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>We are more certain of our judgments than our accuracy usually supports.</t>
+          <t>The tendency to be more confident in our judgments than our actual accuracy usually supports.</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -3296,6 +3551,16 @@
       <c r="H58" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Dunning-Kruger Effect, Optimism Bias</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Overconfidence_effect</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -3310,7 +3575,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>We assume a new tool or change will help more than it does, and overlook its limits.</t>
+          <t>The tendency to assume a new idea, tool, or innovation will help more than it will, while underestimating its limits and side effects.</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -3336,6 +3601,16 @@
       <c r="H59" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Authority Bias</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pro-innovation_bias</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -3350,7 +3625,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>We reject new evidence or ideas because they challenge established norms or beliefs.</t>
+          <t>The tendency to reject new evidence or ideas mainly because they challenge established beliefs, habits, or authority.</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -3376,6 +3651,16 @@
       <c r="H60" s="11" t="n">
         <v>3</v>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Belief Perseverance, Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semmelweis_reflex</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -3390,7 +3675,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>We take more risks when we feel safer, partly offsetting the protection we gained.</t>
+          <t>The tendency to take greater risks when we feel protected, which can partly cancel out the safety we gained.</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -3415,6 +3700,16 @@
       </c>
       <c r="H61" s="11" t="n">
         <v>3</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Illusion of Control</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Risk_compensation</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/second-thought/data/source/cognitive_bias_trainer.xlsx
+++ b/second-thought/data/source/cognitive_bias_trainer.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Categories" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Bias Statistics" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bias Library'!$A$1:$J$61</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -93,8 +95,15 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +114,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5233"/>
         <bgColor rgb="FF333300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +161,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -210,6 +229,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -308,22 +330,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BiasLibrary" displayName="BiasLibrary" ref="A1:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G21"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="bias_id"/>
-    <tableColumn id="2" name="Bias"/>
-    <tableColumn id="3" name="Definition"/>
-    <tableColumn id="4" name="Category"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Everyday Tip"/>
-    <tableColumn id="7" name="Common Contexts"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ChallengeLibrary" displayName="ChallengeLibrary" ref="A1:O61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ChallengeLibrary" displayName="ChallengeLibrary" ref="A1:O61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:O61"/>
   <tableColumns count="15">
     <tableColumn id="1" name="challenge_id"/>
@@ -345,8 +352,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Categories" displayName="Categories" ref="A1:B13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Categories" displayName="Categories" ref="A1:B13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:B13"/>
   <tableColumns count="2">
     <tableColumn id="1" name="category_id"/>
@@ -355,8 +362,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BiasStatistics" displayName="BiasStatistics" ref="A1:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BiasStatistics" displayName="BiasStatistics" ref="A1:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:G21"/>
   <tableColumns count="7">
     <tableColumn id="1" name="bias_id"/>
@@ -547,3160 +554,3241 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" style="11" min="1" max="1"/>
+    <col width="110" customWidth="1" style="12" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Cognitive Bias Trainer — Content Database</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="7.5" customHeight="1" s="12">
-      <c r="A2" s="14" t="n"/>
-    </row>
-    <row r="3" ht="33.75" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>This workbook is the content backbone for a Duolingo-style app that teaches cognitive biases through quizzes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="7.5" customHeight="1" s="12">
-      <c r="A4" s="14" t="n"/>
-    </row>
-    <row r="5" ht="33.75" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Sheet 1 — Bias Library: the master list of biases (one row per bias). Everything else references bias_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33.75" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Sheet 2 — Challenge Library: the quiz questions. Each row is one multiple-choice challenge linked to a bias_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33.75" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Sheet 3 — Categories: the lookup list used to filter/tag biases and contexts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33.75" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Sheet 4 — Bias Statistics: auto-calculated counts (formulas, not hardcoded) showing how many challenges exist per bias, and the breakdown by difficulty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="7.5" customHeight="1" s="12">
-      <c r="A9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="33.75" customHeight="1" s="12">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Current coverage: 20 biases x 3 challenges each = 60 challenges, spread across Recognition / Application / Ambiguous difficulty, and across real-world contexts (Politics, Work, Finance, Health, Media, Relationships, Social Media, Sport, Everyday life...).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="7.5" customHeight="1" s="12">
-      <c r="A11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="33.75" customHeight="1" s="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Each challenge includes: statement, 4 options, correct answer, explanation, a reflection question, why humans do this, real-world context, difficulty, and a Learning Objective — so every question teaches a thinking habit, not just a vocabulary term.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="7.5" customHeight="1" s="12">
-      <c r="A13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="33.75" customHeight="1" s="12">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>To grow this later: duplicate a row in Challenge Library, give it a new challenge_id, set the same bias_id, and fill in new content (by hand or AI-generated). Bias Statistics will update automatically.</t>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Second Thought — Content Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>This Excel file is the source of truth for quiz content. Edit here, then regenerate JSON with:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python3 second-thought/scripts/convert-excel.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1) Bias Library — one row per bias (60 total across Beginner / Intermediate / Advanced tiers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2) Challenge Library — quiz questions (180 total: 3 per bias). Statements are wrapped in quotation marks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3) Categories — lookup list for bias categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4) Bias Statistics — counts of challenges per bias (formulas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bias Library columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- bias_id, Bias, Tier, Category — identity and level (Tier 1=Beginner, 2=Intermediate, 3=Advanced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- Description, Everyday Tip, Common Contexts — supporting teaching notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- Definition, Confused With, Further Reading — LEARN MORE fields (optional depth after an answer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Learn more fields (all 60 biases filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- Definition: fuller, more precise wording of the bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>- Confused With: related bias names from this library (names only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Further Reading: Wikipedia URL for optional deeper reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Challenge Library notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>- Each challenge links to a bias_id and includes statement, 4 options, correct answer,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  explanation, reflection question, why humans do this, context, difficulty, learning objective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Coverage: 60 biases × 3 challenges = 180 questions.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J61"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="11" min="1" max="1"/>
-    <col width="26" customWidth="1" style="11" min="2" max="2"/>
-    <col width="46" customWidth="1" style="11" min="3" max="3"/>
-    <col width="18" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="42" customWidth="1" style="11" min="6" max="6"/>
-    <col width="34" customWidth="1" style="11" min="7" max="7"/>
+    <col width="10" customWidth="1" style="12" min="1" max="1"/>
+    <col width="28" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6" customWidth="1" style="12" min="3" max="3"/>
+    <col width="16" customWidth="1" style="12" min="4" max="4"/>
+    <col width="40" customWidth="1" style="12" min="5" max="5"/>
+    <col width="36" customWidth="1" style="12" min="6" max="6"/>
+    <col width="28" customWidth="1" style="12" min="7" max="7"/>
+    <col width="48" customWidth="1" style="12" min="8" max="8"/>
+    <col width="36" customWidth="1" style="12" min="9" max="9"/>
+    <col width="40" customWidth="1" style="12" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="12">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>bias_id</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>Everyday Tip</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>Common Contexts</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>Everyday Tip</t>
-        </is>
-      </c>
-      <c r="G1" s="18" t="inlineStr">
-        <is>
-          <t>Common Contexts</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="I1" s="11" t="inlineStr">
-        <is>
-          <t>Usually Confused With</t>
-        </is>
-      </c>
-      <c r="J1" s="11" t="inlineStr">
-        <is>
-          <t>Further Reading URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1" s="12">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>Confused With</t>
+        </is>
+      </c>
+      <c r="J1" s="25" t="inlineStr">
+        <is>
+          <t>Further Reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>B001</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Confirmation Bias</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Confirmation bias leads people to favor information that supports what they already think, while ignoring or downplaying evidence that contradicts it.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Before forming an opinion, actively seek out one source that disagrees with you.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Politics, Investing, Relationships, News, Health, Social Media</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>The tendency to seek, interpret, favour, and remember information that supports what we already believe, while giving less weight to information that challenges it.</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Belief Perseverance, Choice-Supportive Bias</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Confirmation_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anchoring Bias</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>Confirmation bias leads people to favor information that supports what they already think, while ignoring or downplaying evidence that contradicts it.</t>
-        </is>
-      </c>
-      <c r="F2" s="19" t="inlineStr">
-        <is>
-          <t>Before forming an opinion, actively seek out one source that disagrees with you.</t>
-        </is>
-      </c>
-      <c r="G2" s="19" t="inlineStr">
-        <is>
-          <t>Politics, Investing, Relationships, News, Health, Social Media</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Once an anchor is set, later judgments are made by adjusting away from it, but the adjustment is usually insufficient.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>When negotiating, try to set your own reference point first instead of reacting to the other side's opening number.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Negotiation, Shopping, Salary discussions, Real estate, Everyday life</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The tendency to rely too heavily on an initial piece of information (an “anchor”) when making estimates or decisions, even when that starting point is arbitrary.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Framing Effect</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Anchoring_(cognitive_bias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Belief Perseverance, Choice-Supportive Bias</t>
-        </is>
-      </c>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Confirmation_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1" s="12">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>B002</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>Anchoring Bias</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to rely too heavily on an initial piece of information (an “anchor”) when making estimates or decisions, even when that starting point is arbitrary.</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>Once an anchor is set, later judgments are made by adjusting away from it, but the adjustment is usually insufficient.</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>When negotiating, try to set your own reference point first instead of reacting to the other side's opening number.</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="inlineStr">
-        <is>
-          <t>Negotiation, Shopping, Salary discussions, Real estate, Everyday life</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vivid, recent, or emotionally charged events are recalled more easily, so we overestimate how common they are.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Check statistics instead of relying on memorable stories when estimating risk.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Media, Health, Safety, Everyday life, News</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A mental shortcut where we judge how common or likely something is by how easily examples come to mind, which can make vivid or recent events feel more frequent than they are.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Recency Bias, Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Availability_heuristic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>When explaining someone else's actions we overweight personality traits and underweight situational factors, but we do the opposite for ourselves.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Before judging someone's behavior, ask what situational pressures might explain it.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Driving, Social situations</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The tendency to explain other people’s actions mainly by their character or personality, while underestimating the role of the situation they are in.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Actor-Observer Bias, Hostile Attribution Bias</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fundamental_attribution_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Self-serving Bias</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>This bias protects self-esteem by crediting ourselves for good outcomes while blaming outside factors for bad ones.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>When something goes wrong, ask honestly what part, if any, was within your control.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Work, Sport, Academics, Relationships</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The tendency to credit our successes to our own ability or effort, and to blame our failures on outside circumstances, bad luck, or other people.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Actor-Observer Bias, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Self-serving_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sunk Cost Fallacy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Past costs (time, money, effort) that cannot be recovered still influence decisions, even though only future costs and benefits should matter.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask: 'if I hadn't invested anything yet, would I still choose to start this today?'</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Finance, Relationships, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>The tendency to continue with a plan or investment because of what we have already put in (time, money, or effort), rather than because future benefits still justify it.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Loss Aversion, Status Quo Bias, Endowment Effect</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sunk_cost#Loss_aversion_and_the_sunk_cost_fallacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Negativity Bias</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Emotion</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bad events, criticism, or emotions tend to have a bigger impact on our mood, memory, and decisions than good ones.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>When reviewing feedback, deliberately count the positive points as well as the negative ones.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Media, Self-awareness</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The tendency for negative events, information, or emotions to affect us more strongly than positive ones of equal intensity.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Loss Aversion</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Negativity_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Halo Effect</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>If someone is attractive, likeable, or competent in one area, we tend to assume they're good in unrelated areas too.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Evaluate people's specific skills and claims separately from your overall impression of them.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Work, Media, Social situations, Politics</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>When a positive overall impression of someone (or something) spills over and makes us rate their other traits more favourably than the evidence supports.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Horn Effect, Authority Bias</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Halo_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Horn Effect</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A single flaw or bad first impression can unfairly color our judgment of someone's other, unrelated qualities.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>When you notice a negative first impression, pause and check if you're generalizing unfairly.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Work, Social situations, Media</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>When a negative overall impression of someone (or something) spills over and makes us rate their other traits more harshly than the evidence supports.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Halo Effect</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Horn_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Survivorship Bias</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Because failures are often invisible or unreported, we draw conclusions from an incomplete, success-only sample.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>When hearing a success story, actively ask how many people tried the same thing and failed.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Work, Media, Finance, Learning</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible — which can distort what we think works.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Survivorship_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hindsight Bias</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Once we know the outcome, our memory of our own earlier predictions shifts to seem more accurate than they really were.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Write predictions down beforehand so you can honestly check them against what you actually said.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Finance, Sport, Politics, Work</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The tendency, after an outcome is known, to see it as more predictable than it really was, and to believe we “knew it all along.”</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hindsight_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>False Consensus Effect</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>This bias makes our own views feel more common or 'normal' than they actually are in the wider population.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Before assuming your opinion is the majority view, ask how you would actually know that.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Politics, Social Media, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how widely others share our beliefs, preferences, and behaviours.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>In-group Bias, Naive Realism</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/False_consensus_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>In-group Bias</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>This bias leads to more trust, generosity, and positive judgment toward people we see as 'us' compared to 'them.'</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>When evaluating people from a different group, ask if you'd judge the same behavior differently coming from your own group.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Work, Politics, Sport, Social situations</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>The tendency to favour people who belong to our own group — giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Out-group Homogeneity Bias, False Consensus Effect</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/In-group_favoritism</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Out-group Homogeneity Bias</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>This bias leads to stereotyping, since we assume 'they're all the same' about outsiders while recognizing individuality within our own group.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>When you catch yourself thinking 'they're all like that,' pause and ask if you'd say the same about your own group.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Work, Social situations, Politics, Media</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>The tendency to see people in other groups as more alike than they are, while seeing members of our own group as more varied and individual.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>In-group Bias, Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Out-group_homogeneity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Framing Effect</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Anchoring_(cognitive_bias)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1" s="12">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>B003</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The same statistic or choice can lead to different decisions depending on whether it's framed in terms of gains or losses.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Try restating a choice in the opposite frame (gain vs. loss) before deciding.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Health, Finance, Marketing, Politics</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented — for example as gains versus losses.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Anchoring Bias, Loss Aversion</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Framing_effect_(psychology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Loss Aversion</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>This asymmetry means people often make decisions to avoid losses rather than to pursue equivalent gains.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>When facing a risky decision, ask whether you're avoiding a loss out of proportion to what you'd actually miss.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Finance, Negotiation, Everyday life, Work</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>The tendency for losses to feel more painful than gains of the same size feel rewarding, which can make us overly cautious about potential losses.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sunk Cost Fallacy, Endowment Effect, Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Loss_aversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optimism Bias</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Self-awareness</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>This bias makes people believe they are less likely than others to experience negative outcomes like illness, accidents, or failure.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>When planning, ask what would happen if things went worse than expected, not just as planned.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Health, Finance, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how likely good things are to happen to us, and to underestimate our personal risk of bad outcomes compared with other people.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect, Planning Fallacy, Illusion of Control</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Optimism_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Status Quo Bias</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>This bias makes people resist switching to new options, defaulting instead to whatever is already in place.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>When comparing the current option to a new one, imagine you were choosing between them fresh, with no history.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Work, Finance, Everyday life, Politics</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>The tendency to prefer the current state of affairs and to treat “keeping things as they are” as the default choice, even when change might be better.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sunk Cost Fallacy, Endowment Effect, Normalcy Bias</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Status_quo_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dunning-Kruger Effect</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Self-awareness</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A little knowledge can create unearned confidence, while true experts are often more aware of what they don't know.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Before feeling confident about a new skill, ask an actual expert to check your assumptions.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Work, Learning, Everyday life, Health</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>A pattern where people with limited skill or knowledge in an area overestimate how competent they are, partly because the same gaps that cause mistakes also hide those mistakes from view.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dunning%E2%80%93Kruger_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Authority Bias</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A person's title, uniform, or perceived status can make their claims seem more credible, even without supporting evidence.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Evaluate a claim by its evidence, then separately consider whether the source's authority is actually relevant to that claim.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Work, Health, Media, Politics</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>The tendency to trust or follow the views of someone seen as an authority more than the strength of their arguments alone would justify.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Halo Effect, Bandwagon Effect</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Authority_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Planning Fallacy</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Even with past experience of delays, we often believe this time will be different and plan too optimistically.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>When estimating time, look at how long similar tasks actually took — not how long you hoped they would take.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Work, Everyday life, Learning, Health</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The tendency to underestimate how long a task will take and how many obstacles will appear, even when similar tasks have overrun before.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Planning_fallacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Recency Bias</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>The latest example feels freshest and can overshadow a longer track record of evidence.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Before deciding, ask what the full history shows — not just the last week.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Work, Finance, Relationships, Media</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The tendency to give recent information more weight than older information, even when the longer track record is more informative.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Availability Heuristic</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>A mental shortcut where we judge how common or likely something is by how easily examples come to mind, which can make vivid or recent events feel more frequent than they are.</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Recency_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bandwagon Effect</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Popularity can feel like proof, even when we have not checked the reasons ourselves.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Before joining in, ask whether you would still choose this if nobody else were doing it.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Social Media, Work, Politics, Everyday life</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>The tendency to adopt a belief or behaviour because many other people are doing so, treating popularity as a signal that it must be right.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Authority Bias, In-group Bias</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bandwagon_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mere Exposure Effect</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Familiarity can create warmth and preference, even without new reasons to prefer something.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Notice when you like something mainly because it feels familiar — not because you have compared it fairly.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Relationships, Media, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>The tendency to like people, ideas, or things more simply because we have encountered them before, even without stronger reasons to prefer them.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Status Quo Bias, Illusory Truth Effect</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mere-exposure_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Endowment Effect</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ownership changes how much something feels worth, compared with an identical item we do not own.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>When selling or keeping something, ask what you would pay for it today if you did not already have it.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Finance, Everyday life, Work, Negotiation</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The tendency to value something more highly once we own it than we would if the same item belonged to someone else.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Loss Aversion, Status Quo Bias, Sunk Cost Fallacy</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Endowment_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gambler's Fallacy</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>Vivid, recent, or emotionally charged events are recalled more easily, so we overestimate how common they are.</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>Check statistics instead of relying on memorable stories when estimating risk.</t>
-        </is>
-      </c>
-      <c r="G4" s="19" t="inlineStr">
-        <is>
-          <t>Media, Health, Safety, Everyday life, News</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Recency Bias, Representativeness Heuristic</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Availability_heuristic</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1" s="12">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>B004</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Fundamental Attribution Error</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to explain other people’s actions mainly by their character or personality, while underestimating the role of the situation they are in.</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Independent random events do not 'make up' for earlier results, but it can feel like they should.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ask whether each new event is truly independent — or whether you are expecting a pattern that randomness does not owe you.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Everyday life, Finance, Sport, Decision Making</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>The belief that a random event is “due” after a streak of opposite outcomes, as if chance keeps a short-run balance sheet.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Clustering Illusion, Illusion of Control</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Gambler%27s_fallacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Clustering Illusion</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A short streak of similar outcomes can feel like a signal, even when it is just noise.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Before calling something a pattern, ask how much data you really have.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Work, Health, Sport, Everyday life</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>The tendency to see meaningful patterns or streaks in small samples of random or unrelated events.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Gambler's Fallacy, Illusory Correlation</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Clustering_illusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>A good story or familiar type can feel more probable than the base rate suggests.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>When a description feels like a perfect fit, check the real frequency before deciding.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Work, Learning, Media, Everyday life</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>A mental shortcut where we judge probability by how much something resembles a familiar stereotype or story, instead of using actual base rates.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Base Rate Neglect, Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Representativeness_heuristic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Base Rate Neglect</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A striking example can overpower the broader statistic about how common something really is.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Start with how often something happens in general, then adjust — not the other way around.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Health, Media, Work, Finance</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>The tendency to ignore general statistical information about how common something is, and to focus instead on specific, vivid details.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Representativeness Heuristic, Availability Heuristic</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Base_rate_fallacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Peak-End Rule</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Emotion</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A strong ending or peak moment can reshape memory more than hours of ordinary experience.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>When recalling an event, ask what happened in the middle — not only the highlight or the finish.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Relationships, Health, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>The tendency to judge an experience mainly by its most intense moment and how it ended, rather than by the whole duration.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Peak%E2%80%93end_rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Choice-Supportive Bias</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Once we commit, our memory and judgment tilt toward making that choice look wiser.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>After buying or deciding, ask what you would say to a friend making the same choice fresh today.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Finance, Relationships, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>The tendency, after we have chosen an option, to remember it more favourably and to downplay its downsides or the appeal of alternatives.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Confirmation Bias, Cognitive Dissonance</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Choice-supportive_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Illusion of Control</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Self-awareness</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Small actions can feel like they are steering big results, even when they are not.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ask which parts of the outcome you can actually affect — and which parts are luck or other people.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Everyday life, Work, Health, Finance</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how much influence our actions have over outcomes that are largely random or outside our control.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Gambler's Fallacy</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusion_of_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spotlight Effect</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>When explaining someone else's actions we overweight personality traits and underweight situational factors, but we do the opposite for ourselves.</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>Before judging someone's behavior, ask what situational pressures might explain it.</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Driving, Social situations</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>Actor-Observer Bias, Hostile Attribution Bias</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Fundamental_attribution_error</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1" s="12">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>B005</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Self-serving Bias</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to credit our successes to our own ability or effort, and to blame our failures on outside circumstances, bad luck, or other people.</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>We are each at the centre of our own attention, but others are usually paying far less attention to us.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>When you feel painfully visible, ask what you would think if a friend did the same thing.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Everyday life, Learning</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how much other people notice our appearance, mistakes, or behaviour.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Illusion of Transparency, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Spotlight_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cognitive Dissonance</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Emotion</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mental discomfort pushes us to justify, minimise, or reframe what we did so it fits who we think we are.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>When you catch yourself rationalising, ask what belief your action is bumping into.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Health, Relationships, Work, Everyday life</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>The mental discomfort that arises when our actions conflict with our beliefs, often leading us to justify, minimise, or reframe what we did.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Choice-Supportive Bias, Belief Perseverance</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cognitive_dissonance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Belief Perseverance</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Once a belief takes hold, we can defend it with new reasons after the original reasons fall away.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ask what evidence would change your mind — and whether you are still using it honestly.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Politics, Work, Relationships, Media</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>The tendency to hold on to a belief even after the evidence that supported it has been weakened or removed.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Confirmation Bias, Semmelweis Reflex</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Belief_perseverance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Normalcy Bias</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Familiar routines feel stable, so warnings or unusual signs can be brushed aside too easily.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>When something feels 'unthinkable,' ask what you would do if it happened anyway.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Health, Everyday life, Work, Finance</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>The tendency to underestimate the likelihood of serious disruption and to assume that life will continue in the usual way.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Status Quo Bias, Optimism Bias</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Normalcy_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Curse of Knowledge</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Experts and experienced people can explain in ways that skip steps obvious to them but not to beginners.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>When explaining, ask what confused you when you first learned this.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Work, Learning, Relationships, Everyday life</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>The difficulty of remembering what it was like not to know something, which can make experts skip steps that beginners still need.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>False Consensus Effect, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Curse_of_knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Illusory Correlation</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Memorable pairings can feel like cause and effect, especially when we already expect a connection.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Before blaming one thing for another, ask how often the effect happens without the cause.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Health, Everyday life, Work, Relationships</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>The tendency to perceive a relationship between two things when none exists, or to see a stronger link than the evidence supports.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Clustering Illusion, Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusory_correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Conjunction Fallacy</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Extra detail can make a scenario feel more believable, even though specifics always lower the true odds.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ask whether each added detail makes the story more vivid — or actually more probable.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Media, Work, Learning, Everyday life</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The tendency to judge a detailed, specific scenario as more probable than a broader one, even though added detail usually makes an event less likely.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Representativeness Heuristic</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Conjunction_fallacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Illusory Truth Effect</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Familiar wording creates a sense of accuracy, whether or not the claim has been verified.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Treat familiarity as a reason to pause — not as proof something is correct.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Media, Politics, Social Media, Health</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The tendency for repeated statements to feel more true, simply because they have become familiar.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Mere Exposure Effect, Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusory_truth_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Actor-Observer Bias</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>This bias protects self-esteem by crediting ourselves for good outcomes while blaming outside factors for bad ones.</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>When something goes wrong, ask honestly what part, if any, was within your control.</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>Work, Sport, Academics, Relationships</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Actor-Observer Bias, Egocentric Bias</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Self-serving_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1" s="12">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>B006</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Sunk Cost Fallacy</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to continue with a plan or investment because of what we have already put in (time, money, or effort), rather than because future benefits still justify it.</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>The same kind of behaviour gets different stories depending on whether we or someone else did it.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>When judging someone else, ask what situation might explain it — the way you would for yourself.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Driving, Everyday life</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>The tendency to explain other people’s behaviour by their character, while explaining our own behaviour by the situation we were in.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error, Self-serving Bias</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Actor%E2%80%93observer_asymmetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bias Blind Spot</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Self-awareness</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>It can feel obvious that other people are skewed, while our own view still feels objective.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>When you spot a bias in someone else, ask where the same pattern might show up in you.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Politics, Everyday life</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>The tendency to recognise cognitive biases more easily in other people than in ourselves.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Naive Realism, Overconfidence Effect</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bias_blind_spot</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Naive Realism</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Our own perspective can feel like plain fact, making disagreement seem like bias or bad faith in others.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>When someone disagrees, ask what they might be seeing that you are not.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Politics, Work, Relationships, Media</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The belief that we see the world objectively, and that people who disagree with us must be uninformed, irrational, or biased.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>False Consensus Effect, Bias Blind Spot</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Na%C3%AFve_realism_(psychology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Just-World Hypothesis</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>The idea of a fair world can make us blame victims or downplay luck and circumstance.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>When something bad happens to someone, notice if you are looking for a reason they 'must have' deserved it.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Media, Relationships, Work, Politics</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>The tendency to assume the world is fair and that people usually get what they deserve, which can lead us to blame victims or downplay luck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error, Hindsight Bias</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Just-world_hypothesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Hostile Attribution Bias</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>A neutral tone, delay, or mistake can be read as personal attack when the intent is unclear.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Before assuming someone meant harm, ask what neutral explanation would also fit.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Relationships, Work, Everyday life, Social Media</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>The tendency to interpret ambiguous actions from others as intentionally hostile, unkind, or personally directed.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Fundamental Attribution Error, Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hostile_attribution_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Self-awareness</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Our contribution, importance, or effort can loom larger in memory than in the shared reality.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>When recalling a group effort, ask what others would say they contributed.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Learning, Everyday life</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>The tendency to remember our own role, effort, or importance in joint events as larger than it really was.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Self-serving Bias, Spotlight Effect</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Egocentric_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Illusion of Transparency</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Social Judgement</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>What feels obvious inside can be nearly invisible outside, but we often assume people can tell.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>If something matters, say it plainly — do not assume your feelings are showing clearly.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Learning, Everyday life</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how easily other people can read our emotions, thoughts, or internal state.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Spotlight Effect, Egocentric Bias</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Illusion_of_transparency</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hyperbolic Discounting</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>Past costs (time, money, effort) that cannot be recovered still influence decisions, even though only future costs and benefits should matter.</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>Ask: 'if I hadn't invested anything yet, would I still choose to start this today?'</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>Finance, Relationships, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>Loss Aversion, Status Quo Bias, Endowment Effect</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Sunk_cost#Loss_aversion_and_the_sunk_cost_fallacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1" s="12">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>B007</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Negativity Bias</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>The tendency for negative events, information, or emotions to affect us more strongly than positive ones of equal intensity.</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>The immediate option feels disproportionately attractive compared with a better long-term choice.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ask what future-you would prefer — not only what right-now-you wants.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Finance, Health, Everyday life, Work</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>The tendency to prefer smaller rewards now over larger rewards later, more steeply than a calm long-term plan would suggest.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Restraint Bias</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hyperbolic_discounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ambiguity Effect</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Known risks can feel safer than unknown ones, so we may stick with the familiar gamble.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>When you avoid something because it feels uncertain, ask whether the known option is truly better.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Finance, Work, Health, Everyday life</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>The tendency to avoid options when the probability of a good outcome is unclear, even if those options could be better than a known alternative.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Status Quo Bias, Loss Aversion</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ambiguity_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Identifiable Victim Effect</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Emotion</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>Bad events, criticism, or emotions tend to have a bigger impact on our mood, memory, and decisions than good ones.</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>When reviewing feedback, deliberately count the positive points as well as the negative ones.</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Media, Self-awareness</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Loss Aversion</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Negativity_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1" s="12">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>B008</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>Halo Effect</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>When a positive overall impression of someone (or something) spills over and makes us rate their other traits more favourably than the evidence supports.</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>A single story with a face and name can move us more than numbers describing many people.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Notice when one story is pulling your attention away from the broader scale of a problem.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Media, Politics, Health, Everyday life</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>The tendency to feel and give more help in response to one identifiable person in need than to large groups described only with statistics.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Availability Heuristic, Negativity Bias</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Identifiable_victim_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Restraint Bias</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Self-awareness</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>We predict strong self-control in advance, then struggle when the temptation is actually in front of us.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Plan for the moment of temptation, not the moment of planning.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Health, Everyday life, Finance, Work</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>The tendency to overestimate how well we will resist temptation when the moment actually arrives.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Overconfidence Effect, Optimism Bias</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Restraint_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>B052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Reactance</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Emotion</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Being told what to do can spark resistance, even when the advice is reasonable.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Notice when you are saying no mainly because someone told you yes — or the reverse.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Relationships, Work, Health, Everyday life</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>The tendency to push back when we feel our freedom is being restricted — sometimes by doing the opposite of what we are urged to do.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Status Quo Bias</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Reactance_(psychology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ostrich Effect</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Not looking can feel like relief, even though the issue remains and may grow worse unseen.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>If you are avoiding a number, email, or conversation, ask what you are afraid it will confirm.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Finance, Health, Work, Relationships</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>The tendency to avoid looking at information that might confirm a problem we would rather not face.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Normalcy Bias</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ostrich_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Zero-Sum Bias</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>If someone is attractive, likeable, or competent in one area, we tend to assume they're good in unrelated areas too.</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>Evaluate people's specific skills and claims separately from your overall impression of them.</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>Work, Media, Social situations, Politics</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>Horn Effect, Authority Bias</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Halo_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1" s="12">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>B009</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Horn Effect</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>When a negative overall impression of someone (or something) spills over and makes us rate their other traits more harshly than the evidence supports.</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Success, praise, or opportunity can feel like a fixed pie, making cooperation harder to see.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>When someone else wins, ask whether anything actually came off your plate.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Work, Relationships, Politics, Everyday life</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>The tendency to treat a situation as if one person’s gain must mean another person’s loss, even when both could benefit.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>In-group Bias</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Zero-sum_thinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Moral Luck</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>A single flaw or bad first impression can unfairly color our judgment of someone's other, unrelated qualities.</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>When you notice a negative first impression, pause and check if you're generalizing unfairly.</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>Work, Social situations, Media</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>Halo Effect</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Horn_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1" s="12">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>B010</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Survivorship Bias</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible — which can distort what we think works.</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>The same choice can look wise or reckless depending on results that were not fully in the person's control.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Try judging the decision separately from how lucky the outcome turned out to be.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Work, Driving, Relationships, Everyday life</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>The tendency to judge how good or bad a decision was partly by how lucky or unlucky the outcome turned out to be.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Hindsight Bias, Fundamental Attribution Error</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Moral_luck</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Texas Sharpshooter Fallacy</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>Because failures are often invisible or unreported, we draw conclusions from an incomplete, success-only sample.</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>When hearing a success story, actively ask how many people tried the same thing and failed.</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>Work, Media, Finance, Learning</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>Availability Heuristic</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Survivorship_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1" s="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>B011</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Hindsight Bias</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>The tendency, after an outcome is known, to see it as more predictable than it really was, and to believe we “knew it all along.”</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>Once we know the outcome, our memory of our own earlier predictions shifts to seem more accurate than they really were.</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>Write predictions down beforehand so you can honestly check them against what you actually said.</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>Finance, Sport, Politics, Work</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Patterns can be invented after the fact, making random data look meaningful.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ask whether you are finding a pattern because you looked for it — or because you predicted it beforehand.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Work, Media, Finance, Health</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>The tendency to notice a cluster in data first, then treat that cluster as if it had been predicted — drawing the target after the shots.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Clustering Illusion, Illusory Correlation</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Texas_sharpshooter_fallacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Hindsight_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1" s="12">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>B012</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>False Consensus Effect</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to overestimate how widely others share our beliefs, preferences, and behaviours.</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>This bias makes our own views feel more common or 'normal' than they actually are in the wider population.</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>Before assuming your opinion is the majority view, ask how you would actually know that.</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>Politics, Social Media, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>In-group Bias, Naive Realism</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/False_consensus_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1" s="12">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>B013</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>In-group Bias</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to favour people who belong to our own group — giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>This bias leads to more trust, generosity, and positive judgment toward people we see as 'us' compared to 'them.'</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>When evaluating people from a different group, ask if you'd judge the same behavior differently coming from your own group.</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>Work, Politics, Sport, Social situations</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Out-group Homogeneity Bias, False Consensus Effect</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/In-group_favoritism</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1" s="12">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>B014</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>Out-group Homogeneity Bias</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to see people in other groups as more alike than they are, while seeing members of our own group as more varied and individual.</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>This bias leads to stereotyping, since we assume 'they're all the same' about outsiders while recognizing individuality within our own group.</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>When you catch yourself thinking 'they're all like that,' pause and ask if you'd say the same about your own group.</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>Work, Social situations, Politics, Media</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>In-group Bias, Representativeness Heuristic</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Out-group_homogeneity</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1" s="12">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>B015</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>Framing Effect</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented — for example as gains versus losses.</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>The same statistic or choice can lead to different decisions depending on whether it's framed in terms of gains or losses.</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>Try restating a choice in the opposite frame (gain vs. loss) before deciding.</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>Health, Finance, Marketing, Politics</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Anchoring Bias, Loss Aversion</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Framing_effect_(psychology)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1" s="12">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>B016</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Loss Aversion</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>The tendency for losses to feel more painful than gains of the same size feel rewarding, which can make us overly cautious about potential losses.</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>This asymmetry means people often make decisions to avoid losses rather than to pursue equivalent gains.</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>When facing a risky decision, ask whether you're avoiding a loss out of proportion to what you'd actually miss.</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>Finance, Negotiation, Everyday life, Work</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Sunk Cost Fallacy, Endowment Effect, Negativity Bias</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Loss_aversion</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1" s="12">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>B017</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>Optimism Bias</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to overestimate how likely good things are to happen to us, and to underestimate our personal risk of bad outcomes compared with other people.</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>This bias makes people believe they are less likely than others to experience negative outcomes like illness, accidents, or failure.</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>When planning, ask what would happen if things went worse than expected, not just as planned.</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>Health, Finance, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Overconfidence Effect, Planning Fallacy, Illusion of Control</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Optimism_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1" s="12">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>B018</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>Status Quo Bias</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to prefer the current state of affairs and to treat “keeping things as they are” as the default choice, even when change might be better.</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>This bias makes people resist switching to new options, defaulting instead to whatever is already in place.</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>When comparing the current option to a new one, imagine you were choosing between them fresh, with no history.</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>Work, Finance, Everyday life, Politics</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Sunk Cost Fallacy, Endowment Effect, Normalcy Bias</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Status_quo_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1" s="12">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>B019</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Dunning-Kruger Effect</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>A pattern where people with limited skill or knowledge in an area overestimate how competent they are, partly because the same gaps that cause mistakes also hide those mistakes from view.</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>Self-awareness</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>A little knowledge can create unearned confidence, while true experts are often more aware of what they don't know.</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>Before feeling confident about a new skill, ask an actual expert to check your assumptions.</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>Work, Learning, Everyday life, Health</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Overconfidence Effect</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Dunning%E2%80%93Kruger_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1" s="12">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>B020</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Authority Bias</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>The tendency to trust or follow the views of someone seen as an authority more than the strength of their arguments alone would justify.</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>A person's title, uniform, or perceived status can make their claims seem more credible, even without supporting evidence.</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>Evaluate a claim by its evidence, then separately consider whether the source's authority is actually relevant to that claim.</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>Work, Health, Media, Politics</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Halo Effect, Bandwagon Effect</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Authority_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>B021</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Planning Fallacy</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to underestimate how long a task will take and how many obstacles will appear, even when similar tasks have overrun before.</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Even with past experience of delays, we often believe this time will be different and plan too optimistically.</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>When estimating time, look at how long similar tasks actually took — not how long you hoped they would take.</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>Work, Everyday life, Learning, Health</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Optimism Bias, Overconfidence Effect</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Planning_fallacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>B022</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Recency Bias</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to give recent information more weight than older information, even when the longer track record is more informative.</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>The latest example feels freshest and can overshadow a longer track record of evidence.</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Before deciding, ask what the full history shows — not just the last week.</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>Work, Finance, Relationships, Media</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Availability Heuristic</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Recency_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>B023</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Bandwagon Effect</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to adopt a belief or behaviour because many other people are doing so, treating popularity as a signal that it must be right.</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Popularity can feel like proof, even when we have not checked the reasons ourselves.</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Before joining in, ask whether you would still choose this if nobody else were doing it.</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>Social Media, Work, Politics, Everyday life</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Authority Bias, In-group Bias</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Bandwagon_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>B024</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Mere Exposure Effect</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to like people, ideas, or things more simply because we have encountered them before, even without stronger reasons to prefer them.</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Familiarity can create warmth and preference, even without new reasons to prefer something.</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Notice when you like something mainly because it feels familiar — not because you have compared it fairly.</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>Relationships, Media, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Status Quo Bias, Illusory Truth Effect</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Mere-exposure_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>B025</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Endowment Effect</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to value something more highly once we own it than we would if the same item belonged to someone else.</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Ownership changes how much something feels worth, compared with an identical item we do not own.</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>When selling or keeping something, ask what you would pay for it today if you did not already have it.</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>Finance, Everyday life, Work, Negotiation</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Loss Aversion, Status Quo Bias, Sunk Cost Fallacy</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Endowment_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>B026</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Gambler's Fallacy</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>The belief that a random event is “due” after a streak of opposite outcomes, as if chance keeps a short-run balance sheet.</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Independent random events do not 'make up' for earlier results, but it can feel like they should.</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>Ask whether each new event is truly independent — or whether you are expecting a pattern that randomness does not owe you.</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Everyday life, Finance, Sport, Decision Making</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Clustering Illusion, Illusion of Control</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Gambler%27s_fallacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>B027</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Clustering Illusion</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to see meaningful patterns or streaks in small samples of random or unrelated events.</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>A short streak of similar outcomes can feel like a signal, even when it is just noise.</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>Before calling something a pattern, ask how much data you really have.</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>Work, Health, Sport, Everyday life</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Gambler's Fallacy, Illusory Correlation</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Clustering_illusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>B028</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Representativeness Heuristic</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>A mental shortcut where we judge probability by how much something resembles a familiar stereotype or story, instead of using actual base rates.</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>A good story or familiar type can feel more probable than the base rate suggests.</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>When a description feels like a perfect fit, check the real frequency before deciding.</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>Work, Learning, Media, Everyday life</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Base Rate Neglect, Availability Heuristic</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Representativeness_heuristic</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>B029</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Base Rate Neglect</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to ignore general statistical information about how common something is, and to focus instead on specific, vivid details.</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>A striking example can overpower the broader statistic about how common something really is.</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>Start with how often something happens in general, then adjust — not the other way around.</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Health, Media, Work, Finance</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Representativeness Heuristic, Availability Heuristic</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Base_rate_fallacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>B030</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Peak-End Rule</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to judge an experience mainly by its most intense moment and how it ended, rather than by the whole duration.</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Emotion</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>A strong ending or peak moment can reshape memory more than hours of ordinary experience.</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>When recalling an event, ask what happened in the middle — not only the highlight or the finish.</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Relationships, Health, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Negativity Bias</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Peak%E2%80%93end_rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>B031</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Choice-Supportive Bias</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>The tendency, after we have chosen an option, to remember it more favourably and to downplay its downsides or the appeal of alternatives.</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Once we commit, our memory and judgment tilt toward making that choice look wiser.</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>After buying or deciding, ask what you would say to a friend making the same choice fresh today.</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Finance, Relationships, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Confirmation Bias, Cognitive Dissonance</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Choice-supportive_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>B032</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Illusion of Control</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to overestimate how much influence our actions have over outcomes that are largely random or outside our control.</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Self-awareness</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Small actions can feel like they are steering big results, even when they are not.</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>Ask which parts of the outcome you can actually affect — and which parts are luck or other people.</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Everyday life, Work, Health, Finance</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Optimism Bias, Gambler's Fallacy</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Illusion_of_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>B033</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Spotlight Effect</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to overestimate how much other people notice our appearance, mistakes, or behaviour.</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>We are each at the centre of our own attention, but others are usually paying far less attention to us.</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>When you feel painfully visible, ask what you would think if a friend did the same thing.</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Everyday life, Learning</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Illusion of Transparency, Egocentric Bias</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Spotlight_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>B034</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Cognitive Dissonance</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>The mental discomfort that arises when our actions conflict with our beliefs, often leading us to justify, minimise, or reframe what we did.</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Emotion</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Mental discomfort pushes us to justify, minimise, or reframe what we did so it fits who we think we are.</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>When you catch yourself rationalising, ask what belief your action is bumping into.</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>Health, Relationships, Work, Everyday life</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Choice-Supportive Bias, Belief Perseverance</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Cognitive_dissonance</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>B035</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Belief Perseverance</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to hold on to a belief even after the evidence that supported it has been weakened or removed.</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Once a belief takes hold, we can defend it with new reasons after the original reasons fall away.</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>Ask what evidence would change your mind — and whether you are still using it honestly.</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>Politics, Work, Relationships, Media</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Confirmation Bias, Semmelweis Reflex</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Belief_perseverance</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>B036</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Normalcy Bias</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to underestimate the likelihood of serious disruption and to assume that life will continue in the usual way.</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Familiar routines feel stable, so warnings or unusual signs can be brushed aside too easily.</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>When something feels 'unthinkable,' ask what you would do if it happened anyway.</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>Health, Everyday life, Work, Finance</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Status Quo Bias, Optimism Bias</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Normalcy_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>B037</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Curse of Knowledge</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>The difficulty of remembering what it was like not to know something, which can make experts skip steps that beginners still need.</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Confidence can feel like proof, even when we are wrong surprisingly often.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>When you feel sure, ask what would make you only 70% sure instead of 100%.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Work, Learning, Finance, Everyday life</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>The tendency to be more confident in our judgments than our actual accuracy usually supports.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Dunning-Kruger Effect, Optimism Bias</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Overconfidence_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pro-Innovation Bias</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Novelty can feel like progress by itself, even before evidence shows it works better.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ask what problem the new thing solves — and what it might break.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Work, Health, Learning, Everyday life</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>The tendency to assume a new idea, tool, or innovation will help more than it will, while underestimating its limits and side effects.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Optimism Bias, Authority Bias</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pro-innovation_bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Semmelweis Reflex</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>Experts and experienced people can explain in ways that skip steps obvious to them but not to beginners.</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>When explaining, ask what confused you when you first learned this.</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>Work, Learning, Relationships, Everyday life</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>False Consensus Effect, Egocentric Bias</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Curse_of_knowledge</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>B038</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Illusory Correlation</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to perceive a relationship between two things when none exists, or to see a stronger link than the evidence supports.</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Memorable pairings can feel like cause and effect, especially when we already expect a connection.</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>Before blaming one thing for another, ask how often the effect happens without the cause.</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>Health, Everyday life, Work, Relationships</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Clustering Illusion, Confirmation Bias</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Illusory_correlation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>B039</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Conjunction Fallacy</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to judge a detailed, specific scenario as more probable than a broader one, even though added detail usually makes an event less likely.</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>Extra detail can make a scenario feel more believable, even though specifics always lower the true odds.</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>Ask whether each added detail makes the story more vivid — or actually more probable.</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>Media, Work, Learning, Everyday life</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Representativeness Heuristic</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Conjunction_fallacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>B040</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>Illusory Truth Effect</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>The tendency for repeated statements to feel more true, simply because they have become familiar.</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Familiar wording creates a sense of accuracy, whether or not the claim has been verified.</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>Treat familiarity as a reason to pause — not as proof something is correct.</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>Media, Politics, Social Media, Health</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Mere Exposure Effect, Confirmation Bias</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Illusory_truth_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>B041</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>Actor-Observer Bias</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to explain other people’s behaviour by their character, while explaining our own behaviour by the situation we were in.</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>The same kind of behaviour gets different stories depending on whether we or someone else did it.</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>When judging someone else, ask what situation might explain it — the way you would for yourself.</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Driving, Everyday life</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Familiar ways of doing things can feel safer than unfamiliar evidence, even when the evidence is strong.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>When a new idea feels wrong mainly because it is new, separate that feeling from whether it is actually wrong.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Work, Health, Learning, Politics</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>The tendency to reject new evidence or ideas mainly because they challenge established beliefs, habits, or authority.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Belief Perseverance, Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semmelweis_reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Risk Compensation</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
         <v>3</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Fundamental Attribution Error, Self-serving Bias</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Actor%E2%80%93observer_asymmetry</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>B042</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Bias Blind Spot</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to recognise cognitive biases more easily in other people than in ourselves.</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>Self-awareness</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>It can feel obvious that other people are skewed, while our own view still feels objective.</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>When you spot a bias in someone else, ask where the same pattern might show up in you.</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Politics, Everyday life</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Naive Realism, Overconfidence Effect</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Bias_blind_spot</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>B043</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Naive Realism</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>The belief that we see the world objectively, and that people who disagree with us must be uninformed, irrational, or biased.</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Our own perspective can feel like plain fact, making disagreement seem like bias or bad faith in others.</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>When someone disagrees, ask what they might be seeing that you are not.</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>Politics, Work, Relationships, Media</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>False Consensus Effect, Bias Blind Spot</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Na%C3%AFve_realism_(psychology)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>B044</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>Just-World Hypothesis</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to assume the world is fair and that people usually get what they deserve, which can lead us to blame victims or downplay luck.</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>The idea of a fair world can make us blame victims or downplay luck and circumstance.</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>When something bad happens to someone, notice if you are looking for a reason they 'must have' deserved it.</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>Media, Relationships, Work, Politics</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Fundamental Attribution Error, Hindsight Bias</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Just-world_hypothesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>B045</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>Hostile Attribution Bias</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to interpret ambiguous actions from others as intentionally hostile, unkind, or personally directed.</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>A neutral tone, delay, or mistake can be read as personal attack when the intent is unclear.</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>Before assuming someone meant harm, ask what neutral explanation would also fit.</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>Relationships, Work, Everyday life, Social Media</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Fundamental Attribution Error, Negativity Bias</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Hostile_attribution_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>B046</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>Egocentric Bias</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to remember our own role, effort, or importance in joint events as larger than it really was.</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>Self-awareness</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>Our contribution, importance, or effort can loom larger in memory than in the shared reality.</t>
-        </is>
-      </c>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>When recalling a group effort, ask what others would say they contributed.</t>
-        </is>
-      </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Learning, Everyday life</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Self-serving Bias, Spotlight Effect</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Egocentric_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>B047</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>Illusion of Transparency</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to overestimate how easily other people can read our emotions, thoughts, or internal state.</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>What feels obvious inside can be nearly invisible outside, but we often assume people can tell.</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>If something matters, say it plainly — do not assume your feelings are showing clearly.</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Learning, Everyday life</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Spotlight Effect, Egocentric Bias</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Illusion_of_transparency</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>B048</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Hyperbolic Discounting</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to prefer smaller rewards now over larger rewards later, more steeply than a calm long-term plan would suggest.</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>The immediate option feels disproportionately attractive compared with a better long-term choice.</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>Ask what future-you would prefer — not only what right-now-you wants.</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>Finance, Health, Everyday life, Work</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Optimism Bias, Restraint Bias</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Hyperbolic_discounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>B049</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>Ambiguity Effect</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to avoid options when the probability of a good outcome is unclear, even if those options could be better than a known alternative.</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>Known risks can feel safer than unknown ones, so we may stick with the familiar gamble.</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>When you avoid something because it feels uncertain, ask whether the known option is truly better.</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>Finance, Work, Health, Everyday life</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Status Quo Bias, Loss Aversion</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Ambiguity_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>B050</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Identifiable Victim Effect</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to feel and give more help in response to one identifiable person in need than to large groups described only with statistics.</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>Emotion</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>A single story with a face and name can move us more than numbers describing many people.</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>Notice when one story is pulling your attention away from the broader scale of a problem.</t>
-        </is>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>Media, Politics, Health, Everyday life</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Availability Heuristic, Negativity Bias</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Identifiable_victim_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>B051</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>Restraint Bias</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to overestimate how well we will resist temptation when the moment actually arrives.</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Self-awareness</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>We predict strong self-control in advance, then struggle when the temptation is actually in front of us.</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>Plan for the moment of temptation, not the moment of planning.</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>Health, Everyday life, Finance, Work</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Overconfidence Effect, Optimism Bias</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Restraint_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>B052</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>Reactance</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to push back when we feel our freedom is being restricted — sometimes by doing the opposite of what we are urged to do.</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Emotion</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>Being told what to do can spark resistance, even when the advice is reasonable.</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>Notice when you are saying no mainly because someone told you yes — or the reverse.</t>
-        </is>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>Relationships, Work, Health, Everyday life</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Status Quo Bias</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Reactance_(psychology)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>B053</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>Ostrich Effect</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to avoid looking at information that might confirm a problem we would rather not face.</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>Not looking can feel like relief, even though the issue remains and may grow worse unseen.</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>If you are avoiding a number, email, or conversation, ask what you are afraid it will confirm.</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>Finance, Health, Work, Relationships</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Optimism Bias, Normalcy Bias</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Ostrich_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>B054</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>Zero-Sum Bias</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to treat a situation as if one person’s gain must mean another person’s loss, even when both could benefit.</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Success, praise, or opportunity can feel like a fixed pie, making cooperation harder to see.</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>When someone else wins, ask whether anything actually came off your plate.</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>Work, Relationships, Politics, Everyday life</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>In-group Bias</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Zero-sum_thinking</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>B055</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>Moral Luck</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to judge how good or bad a decision was partly by how lucky or unlucky the outcome turned out to be.</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>Social Judgement</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>The same choice can look wise or reckless depending on results that were not fully in the person's control.</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>Try judging the decision separately from how lucky the outcome turned out to be.</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>Work, Driving, Relationships, Everyday life</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Hindsight Bias, Fundamental Attribution Error</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Moral_luck</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>B056</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Texas Sharpshooter Fallacy</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to notice a cluster in data first, then treat that cluster as if it had been predicted — drawing the target after the shots.</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>Patterns can be invented after the fact, making random data look meaningful.</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>Ask whether you are finding a pattern because you looked for it — or because you predicted it beforehand.</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>Work, Media, Finance, Health</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Clustering Illusion, Illusory Correlation</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Texas_sharpshooter_fallacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>B057</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>Overconfidence Effect</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to be more confident in our judgments than our actual accuracy usually supports.</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>Self-awareness</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>Confidence can feel like proof, even when we are wrong surprisingly often.</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>When you feel sure, ask what would make you only 70% sure instead of 100%.</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>Work, Learning, Finance, Everyday life</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Dunning-Kruger Effect, Optimism Bias</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Overconfidence_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>B058</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Pro-Innovation Bias</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to assume a new idea, tool, or innovation will help more than it will, while underestimating its limits and side effects.</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>Novelty can feel like progress by itself, even before evidence shows it works better.</t>
-        </is>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
-        <is>
-          <t>Ask what problem the new thing solves — and what it might break.</t>
-        </is>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>Work, Health, Learning, Everyday life</t>
-        </is>
-      </c>
-      <c r="H59" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Optimism Bias, Authority Bias</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Pro-innovation_bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>B059</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>Semmelweis Reflex</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>The tendency to reject new evidence or ideas mainly because they challenge established beliefs, habits, or authority.</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>Familiar ways of doing things can feel safer than unfamiliar evidence, even when the evidence is strong.</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>When a new idea feels wrong mainly because it is new, separate that feeling from whether it is actually wrong.</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>Work, Health, Learning, Politics</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Belief Perseverance, Confirmation Bias</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Semmelweis_reflex</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>B060</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Risk Compensation</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Extra safety can lead to looser behaviour, so the overall risk may not fall as much as expected.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>When a safety measure makes you feel protected, ask whether you are relaxing in ways that bring risk back.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Health, Driving, Everyday life, Work</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>The tendency to take greater risks when we feel protected, which can partly cancel out the safety we gained.</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>Extra safety can lead to looser behaviour, so the overall risk may not fall as much as expected.</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>When a safety measure makes you feel protected, ask whether you are relaxing in ways that bring risk back.</t>
-        </is>
-      </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>Health, Driving, Everyday life, Work</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>Optimism Bias, Illusion of Control</t>
@@ -3713,12 +3801,8 @@
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <autoFilter ref="A1:J61"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/second-thought/data/source/cognitive_bias_trainer.xlsx
+++ b/second-thought/data/source/cognitive_bias_trainer.xlsx
@@ -567,156 +567,156 @@
     <row r="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>Second Thought — Content Database</t>
+          <t>Second Thought: Content Database</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>This Excel file is the source of truth for quiz content. Edit here, then regenerate JSON with:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  python3 second-thought/scripts/convert-excel.py</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1) Bias Library — one row per bias (60 total across Beginner / Intermediate / Advanced tiers).</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>1) Bias Library: one row per bias (60 total across Beginner / Intermediate / Advanced tiers).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2) Challenge Library — quiz questions (180 total: 3 per bias). Statements are wrapped in quotation marks.</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>2) Challenge Library: quiz questions (180 total: 3 per bias). Statements are wrapped in quotation marks.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3) Categories — lookup list for bias categories.</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>3) Categories: lookup list for bias categories.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>4) Bias Statistics — counts of challenges per bias (formulas).</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>4) Bias Statistics: counts of challenges per bias (formulas).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Bias Library columns</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- bias_id, Bias, Tier, Category — identity and level (Tier 1=Beginner, 2=Intermediate, 3=Advanced)</t>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>- bias_id, Bias, Tier, Category: identity and level (Tier 1=Beginner, 2=Intermediate, 3=Advanced)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- Description, Everyday Tip, Common Contexts — supporting teaching notes</t>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>- Description, Everyday Tip, Common Contexts: supporting teaching notes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- Definition, Confused With, Further Reading — LEARN MORE fields (optional depth after an answer)</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>- Definition, Confused With, Further Reading: LEARN MORE fields (optional depth after an answer)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Learn more fields (all 60 biases filled)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>- Definition: fuller, more precise wording of the bias</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>- Confused With: related bias names from this library (names only)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>- Further Reading: Wikipedia URL for optional deeper reading</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Challenge Library notes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>- Each challenge links to a bias_id and includes statement, 4 options, correct answer,</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  explanation, reflection question, why humans do this, context, difficulty, learning objective.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Coverage: 60 biases × 3 challenges = 180 questions.</t>
         </is>
@@ -801,3000 +801,3000 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>B001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Confirmation Bias</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Confirmation bias leads people to favor information that supports what they already think, while ignoring or downplaying evidence that contradicts it.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Before forming an opinion, actively seek out one source that disagrees with you.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Politics, Investing, Relationships, News, Health, Social Media</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>The tendency to seek, interpret, favour, and remember information that supports what we already believe, while giving less weight to information that challenges it.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>Belief Perseverance, Choice-Supportive Bias</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Confirmation_bias</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>B002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Anchoring Bias</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Once an anchor is set, later judgments are made by adjusting away from it, but the adjustment is usually insufficient.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>When negotiating, try to set your own reference point first instead of reacting to the other side's opening number.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Negotiation, Shopping, Salary discussions, Real estate, Everyday life</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>The tendency to rely too heavily on an initial piece of information (an “anchor”) when making estimates or decisions, even when that starting point is arbitrary.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>Framing Effect</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Anchoring_(cognitive_bias)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>B003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Availability Heuristic</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Vivid, recent, or emotionally charged events are recalled more easily, so we overestimate how common they are.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Check statistics instead of relying on memorable stories when estimating risk.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Media, Health, Safety, Everyday life, News</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>A mental shortcut where we judge how common or likely something is by how easily examples come to mind, which can make vivid or recent events feel more frequent than they are.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>Recency Bias, Representativeness Heuristic</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Availability_heuristic</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>B004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Fundamental Attribution Error</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>When explaining someone else's actions we overweight personality traits and underweight situational factors, but we do the opposite for ourselves.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Before judging someone's behavior, ask what situational pressures might explain it.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Driving, Social situations</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>The tendency to explain other people’s actions mainly by their character or personality, while underestimating the role of the situation they are in.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>Actor-Observer Bias, Hostile Attribution Bias</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Fundamental_attribution_error</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>B005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Self-serving Bias</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>This bias protects self-esteem by crediting ourselves for good outcomes while blaming outside factors for bad ones.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>When something goes wrong, ask honestly what part, if any, was within your control.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Work, Sport, Academics, Relationships</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>The tendency to credit our successes to our own ability or effort, and to blame our failures on outside circumstances, bad luck, or other people.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Actor-Observer Bias, Egocentric Bias</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Self-serving_bias</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>B006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Sunk Cost Fallacy</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Past costs (time, money, effort) that cannot be recovered still influence decisions, even though only future costs and benefits should matter.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Ask: 'if I hadn't invested anything yet, would I still choose to start this today?'</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Finance, Relationships, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>The tendency to continue with a plan or investment because of what we have already put in (time, money, or effort), rather than because future benefits still justify it.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>Loss Aversion, Status Quo Bias, Endowment Effect</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Sunk_cost#Loss_aversion_and_the_sunk_cost_fallacy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>B007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Negativity Bias</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Emotion</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Bad events, criticism, or emotions tend to have a bigger impact on our mood, memory, and decisions than good ones.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>When reviewing feedback, deliberately count the positive points as well as the negative ones.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Media, Self-awareness</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>The tendency for negative events, information, or emotions to affect us more strongly than positive ones of equal intensity.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>Loss Aversion</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Negativity_bias</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>B008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Halo Effect</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>If someone is attractive, likeable, or competent in one area, we tend to assume they're good in unrelated areas too.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Evaluate people's specific skills and claims separately from your overall impression of them.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Work, Media, Social situations, Politics</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>When a positive overall impression of someone (or something) spills over and makes us rate their other traits more favourably than the evidence supports.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>Horn Effect, Authority Bias</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Halo_effect</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>B009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Horn Effect</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>A single flaw or bad first impression can unfairly color our judgment of someone's other, unrelated qualities.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>When you notice a negative first impression, pause and check if you're generalizing unfairly.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Work, Social situations, Media</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>When a negative overall impression of someone (or something) spills over and makes us rate their other traits more harshly than the evidence supports.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Halo Effect</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Horn_effect</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>B010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Survivorship Bias</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Because failures are often invisible or unreported, we draw conclusions from an incomplete, success-only sample.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>When hearing a success story, actively ask how many people tried the same thing and failed.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Work, Media, Finance, Learning</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible — which can distort what we think works.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to draw conclusions from the people or cases that “made it,” while overlooking those that failed, dropped out, or were never visible, which can distort what we think works.</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>Availability Heuristic</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Survivorship_bias</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>B011</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Hindsight Bias</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Once we know the outcome, our memory of our own earlier predictions shifts to seem more accurate than they really were.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Write predictions down beforehand so you can honestly check them against what you actually said.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Finance, Sport, Politics, Work</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>The tendency, after an outcome is known, to see it as more predictable than it really was, and to believe we “knew it all along.”</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Hindsight_bias</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>B012</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>False Consensus Effect</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>This bias makes our own views feel more common or 'normal' than they actually are in the wider population.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Before assuming your opinion is the majority view, ask how you would actually know that.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Politics, Social Media, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>The tendency to overestimate how widely others share our beliefs, preferences, and behaviours.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>In-group Bias, Naive Realism</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/False_consensus_effect</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>B013</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>In-group Bias</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>This bias leads to more trust, generosity, and positive judgment toward people we see as 'us' compared to 'them.'</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>When evaluating people from a different group, ask if you'd judge the same behavior differently coming from your own group.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Work, Politics, Sport, Social situations</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>The tendency to favour people who belong to our own group — giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to favour people who belong to our own group, giving them more trust, warmth, or benefit of the doubt than we give outsiders.</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>Out-group Homogeneity Bias, False Consensus Effect</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/In-group_favoritism</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>B014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Out-group Homogeneity Bias</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>This bias leads to stereotyping, since we assume 'they're all the same' about outsiders while recognizing individuality within our own group.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>When you catch yourself thinking 'they're all like that,' pause and ask if you'd say the same about your own group.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Work, Social situations, Politics, Media</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>The tendency to see people in other groups as more alike than they are, while seeing members of our own group as more varied and individual.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>In-group Bias, Representativeness Heuristic</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Out-group_homogeneity</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>B015</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Framing Effect</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>The same statistic or choice can lead to different decisions depending on whether it's framed in terms of gains or losses.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Try restating a choice in the opposite frame (gain vs. loss) before deciding.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Health, Finance, Marketing, Politics</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented — for example as gains versus losses.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>The tendency for the same facts to lead to different choices depending on how they are worded or presented, for example as gains versus losses.</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>Anchoring Bias, Loss Aversion</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Framing_effect_(psychology)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>B016</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Loss Aversion</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>This asymmetry means people often make decisions to avoid losses rather than to pursue equivalent gains.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>When facing a risky decision, ask whether you're avoiding a loss out of proportion to what you'd actually miss.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Finance, Negotiation, Everyday life, Work</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>The tendency for losses to feel more painful than gains of the same size feel rewarding, which can make us overly cautious about potential losses.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>Sunk Cost Fallacy, Endowment Effect, Negativity Bias</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Loss_aversion</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>B017</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>This bias makes people believe they are less likely than others to experience negative outcomes like illness, accidents, or failure.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>When planning, ask what would happen if things went worse than expected, not just as planned.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Health, Finance, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>The tendency to overestimate how likely good things are to happen to us, and to underestimate our personal risk of bad outcomes compared with other people.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect, Planning Fallacy, Illusion of Control</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Optimism_bias</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>B018</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Status Quo Bias</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>This bias makes people resist switching to new options, defaulting instead to whatever is already in place.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>When comparing the current option to a new one, imagine you were choosing between them fresh, with no history.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Work, Finance, Everyday life, Politics</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>The tendency to prefer the current state of affairs and to treat “keeping things as they are” as the default choice, even when change might be better.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>Sunk Cost Fallacy, Endowment Effect, Normalcy Bias</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Status_quo_bias</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>B019</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Dunning-Kruger Effect</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>A little knowledge can create unearned confidence, while true experts are often more aware of what they don't know.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Before feeling confident about a new skill, ask an actual expert to check your assumptions.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Work, Learning, Everyday life, Health</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>A pattern where people with limited skill or knowledge in an area overestimate how competent they are, partly because the same gaps that cause mistakes also hide those mistakes from view.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Dunning%E2%80%93Kruger_effect</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>B020</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Authority Bias</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>A person's title, uniform, or perceived status can make their claims seem more credible, even without supporting evidence.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Evaluate a claim by its evidence, then separately consider whether the source's authority is actually relevant to that claim.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Work, Health, Media, Politics</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>The tendency to trust or follow the views of someone seen as an authority more than the strength of their arguments alone would justify.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>Halo Effect, Bandwagon Effect</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Authority_bias</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>B021</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Planning Fallacy</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Even with past experience of delays, we often believe this time will be different and plan too optimistically.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>When estimating time, look at how long similar tasks actually took — not how long you hoped they would take.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>When estimating time, look at how long similar tasks actually took, not how long you hoped they would take.</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Work, Everyday life, Learning, Health</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>The tendency to underestimate how long a task will take and how many obstacles will appear, even when similar tasks have overrun before.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias, Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Planning_fallacy</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>B022</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Recency Bias</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>The latest example feels freshest and can overshadow a longer track record of evidence.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Before deciding, ask what the full history shows — not just the last week.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Before deciding, ask what the full history shows, not just the last week.</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Work, Finance, Relationships, Media</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>The tendency to give recent information more weight than older information, even when the longer track record is more informative.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>Availability Heuristic</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Recency_bias</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>B023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Bandwagon Effect</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Popularity can feel like proof, even when we have not checked the reasons ourselves.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Before joining in, ask whether you would still choose this if nobody else were doing it.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Social Media, Work, Politics, Everyday life</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>The tendency to adopt a belief or behaviour because many other people are doing so, treating popularity as a signal that it must be right.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>Authority Bias, In-group Bias</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Bandwagon_effect</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>B024</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Mere Exposure Effect</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Familiarity can create warmth and preference, even without new reasons to prefer something.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Notice when you like something mainly because it feels familiar — not because you have compared it fairly.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Notice when you like something mainly because it feels familiar, not because you have compared it fairly.</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Relationships, Media, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>The tendency to like people, ideas, or things more simply because we have encountered them before, even without stronger reasons to prefer them.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>Status Quo Bias, Illusory Truth Effect</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Mere-exposure_effect</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>B025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Endowment Effect</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Ownership changes how much something feels worth, compared with an identical item we do not own.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>When selling or keeping something, ask what you would pay for it today if you did not already have it.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Finance, Everyday life, Work, Negotiation</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>The tendency to value something more highly once we own it than we would if the same item belonged to someone else.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>Loss Aversion, Status Quo Bias, Sunk Cost Fallacy</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Endowment_effect</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>B026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Gambler's Fallacy</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Independent random events do not 'make up' for earlier results, but it can feel like they should.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Ask whether each new event is truly independent — or whether you are expecting a pattern that randomness does not owe you.</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Ask whether each new event is truly independent, or whether you are expecting a pattern that randomness does not owe you.</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Everyday life, Finance, Sport, Decision Making</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>The belief that a random event is “due” after a streak of opposite outcomes, as if chance keeps a short-run balance sheet.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>Clustering Illusion, Illusion of Control</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Gambler%27s_fallacy</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>B027</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Clustering Illusion</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>A short streak of similar outcomes can feel like a signal, even when it is just noise.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Before calling something a pattern, ask how much data you really have.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Work, Health, Sport, Everyday life</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>The tendency to see meaningful patterns or streaks in small samples of random or unrelated events.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>Gambler's Fallacy, Illusory Correlation</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Clustering_illusion</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>B028</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Representativeness Heuristic</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>A good story or familiar type can feel more probable than the base rate suggests.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>When a description feels like a perfect fit, check the real frequency before deciding.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Work, Learning, Media, Everyday life</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>A mental shortcut where we judge probability by how much something resembles a familiar stereotype or story, instead of using actual base rates.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>Base Rate Neglect, Availability Heuristic</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Representativeness_heuristic</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>B029</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Base Rate Neglect</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>A striking example can overpower the broader statistic about how common something really is.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Start with how often something happens in general, then adjust — not the other way around.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Start with how often something happens in general, then adjust, not the other way around.</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Health, Media, Work, Finance</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>The tendency to ignore general statistical information about how common something is, and to focus instead on specific, vivid details.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>Representativeness Heuristic, Availability Heuristic</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Base_rate_fallacy</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>B030</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Peak-End Rule</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Emotion</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>A strong ending or peak moment can reshape memory more than hours of ordinary experience.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>When recalling an event, ask what happened in the middle — not only the highlight or the finish.</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>When recalling an event, ask what happened in the middle, not only the highlight or the finish.</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Relationships, Health, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>The tendency to judge an experience mainly by its most intense moment and how it ended, rather than by the whole duration.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>Negativity Bias</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Peak%E2%80%93end_rule</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>B031</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Choice-Supportive Bias</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Once we commit, our memory and judgment tilt toward making that choice look wiser.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>After buying or deciding, ask what you would say to a friend making the same choice fresh today.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Finance, Relationships, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>The tendency, after we have chosen an option, to remember it more favourably and to downplay its downsides or the appeal of alternatives.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>Confirmation Bias, Cognitive Dissonance</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Choice-supportive_bias</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>B032</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Illusion of Control</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Small actions can feel like they are steering big results, even when they are not.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ask which parts of the outcome you can actually affect — and which parts are luck or other people.</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Ask which parts of the outcome you can actually affect, and which parts are luck or other people.</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Everyday life, Work, Health, Finance</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>The tendency to overestimate how much influence our actions have over outcomes that are largely random or outside our control.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias, Gambler's Fallacy</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Illusion_of_control</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>B033</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Spotlight Effect</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>We are each at the centre of our own attention, but others are usually paying far less attention to us.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>When you feel painfully visible, ask what you would think if a friend did the same thing.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Everyday life, Learning</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>The tendency to overestimate how much other people notice our appearance, mistakes, or behaviour.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>Illusion of Transparency, Egocentric Bias</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Spotlight_effect</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>B034</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Cognitive Dissonance</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Emotion</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Mental discomfort pushes us to justify, minimise, or reframe what we did so it fits who we think we are.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>When you catch yourself rationalising, ask what belief your action is bumping into.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Health, Relationships, Work, Everyday life</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>The mental discomfort that arises when our actions conflict with our beliefs, often leading us to justify, minimise, or reframe what we did.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>Choice-Supportive Bias, Belief Perseverance</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Cognitive_dissonance</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>B035</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Belief Perseverance</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Once a belief takes hold, we can defend it with new reasons after the original reasons fall away.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Ask what evidence would change your mind — and whether you are still using it honestly.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Ask what evidence would change your mind, and whether you are still using it honestly.</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>Politics, Work, Relationships, Media</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>The tendency to hold on to a belief even after the evidence that supported it has been weakened or removed.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>Confirmation Bias, Semmelweis Reflex</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Belief_perseverance</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>B036</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Normalcy Bias</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Familiar routines feel stable, so warnings or unusual signs can be brushed aside too easily.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>When something feels 'unthinkable,' ask what you would do if it happened anyway.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Health, Everyday life, Work, Finance</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>The tendency to underestimate the likelihood of serious disruption and to assume that life will continue in the usual way.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>Status Quo Bias, Optimism Bias</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Normalcy_bias</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>B037</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Curse of Knowledge</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Experts and experienced people can explain in ways that skip steps obvious to them but not to beginners.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>When explaining, ask what confused you when you first learned this.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>Work, Learning, Relationships, Everyday life</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>The difficulty of remembering what it was like not to know something, which can make experts skip steps that beginners still need.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>False Consensus Effect, Egocentric Bias</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Curse_of_knowledge</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>B038</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Illusory Correlation</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Memorable pairings can feel like cause and effect, especially when we already expect a connection.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Before blaming one thing for another, ask how often the effect happens without the cause.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Health, Everyday life, Work, Relationships</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>The tendency to perceive a relationship between two things when none exists, or to see a stronger link than the evidence supports.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>Clustering Illusion, Confirmation Bias</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Illusory_correlation</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>B039</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Conjunction Fallacy</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Extra detail can make a scenario feel more believable, even though specifics always lower the true odds.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ask whether each added detail makes the story more vivid — or actually more probable.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Ask whether each added detail makes the story more vivid, or actually more probable.</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>Media, Work, Learning, Everyday life</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>The tendency to judge a detailed, specific scenario as more probable than a broader one, even though added detail usually makes an event less likely.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>Representativeness Heuristic</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Conjunction_fallacy</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>B040</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Illusory Truth Effect</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Familiar wording creates a sense of accuracy, whether or not the claim has been verified.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Treat familiarity as a reason to pause — not as proof something is correct.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Treat familiarity as a reason to pause, not as proof something is correct.</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Media, Politics, Social Media, Health</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>The tendency for repeated statements to feel more true, simply because they have become familiar.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>Mere Exposure Effect, Confirmation Bias</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Illusory_truth_effect</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>B041</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Actor-Observer Bias</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>The same kind of behaviour gets different stories depending on whether we or someone else did it.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>When judging someone else, ask what situation might explain it — the way you would for yourself.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>When judging someone else, ask what situation might explain it, the way you would for yourself.</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Driving, Everyday life</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>The tendency to explain other people’s behaviour by their character, while explaining our own behaviour by the situation we were in.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>Fundamental Attribution Error, Self-serving Bias</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Actor%E2%80%93observer_asymmetry</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>B042</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Bias Blind Spot</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>It can feel obvious that other people are skewed, while our own view still feels objective.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>When you spot a bias in someone else, ask where the same pattern might show up in you.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Politics, Everyday life</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>The tendency to recognise cognitive biases more easily in other people than in ourselves.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>Naive Realism, Overconfidence Effect</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Bias_blind_spot</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>B043</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>Naive Realism</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Our own perspective can feel like plain fact, making disagreement seem like bias or bad faith in others.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>When someone disagrees, ask what they might be seeing that you are not.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>Politics, Work, Relationships, Media</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>The belief that we see the world objectively, and that people who disagree with us must be uninformed, irrational, or biased.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>False Consensus Effect, Bias Blind Spot</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Na%C3%AFve_realism_(psychology)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>B044</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Just-World Hypothesis</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>The idea of a fair world can make us blame victims or downplay luck and circumstance.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>When something bad happens to someone, notice if you are looking for a reason they 'must have' deserved it.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Media, Relationships, Work, Politics</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>The tendency to assume the world is fair and that people usually get what they deserve, which can lead us to blame victims or downplay luck.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>Fundamental Attribution Error, Hindsight Bias</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Just-world_hypothesis</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>B045</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Hostile Attribution Bias</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>A neutral tone, delay, or mistake can be read as personal attack when the intent is unclear.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>Before assuming someone meant harm, ask what neutral explanation would also fit.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>Relationships, Work, Everyday life, Social Media</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>The tendency to interpret ambiguous actions from others as intentionally hostile, unkind, or personally directed.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>Fundamental Attribution Error, Negativity Bias</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Hostile_attribution_bias</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>B046</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Egocentric Bias</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Our contribution, importance, or effort can loom larger in memory than in the shared reality.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>When recalling a group effort, ask what others would say they contributed.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Learning, Everyday life</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>The tendency to remember our own role, effort, or importance in joint events as larger than it really was.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>Self-serving Bias, Spotlight Effect</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Egocentric_bias</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>B047</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>Illusion of Transparency</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>What feels obvious inside can be nearly invisible outside, but we often assume people can tell.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>If something matters, say it plainly — do not assume your feelings are showing clearly.</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>If something matters, say it plainly, do not assume your feelings are showing clearly.</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Learning, Everyday life</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>The tendency to overestimate how easily other people can read our emotions, thoughts, or internal state.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>Spotlight Effect, Egocentric Bias</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Illusion_of_transparency</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>B048</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Hyperbolic Discounting</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>The immediate option feels disproportionately attractive compared with a better long-term choice.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Ask what future-you would prefer — not only what right-now-you wants.</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Ask what future-you would prefer, not only what right-now-you wants.</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Finance, Health, Everyday life, Work</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>The tendency to prefer smaller rewards now over larger rewards later, more steeply than a calm long-term plan would suggest.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias, Restraint Bias</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Hyperbolic_discounting</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>B049</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>Ambiguity Effect</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Known risks can feel safer than unknown ones, so we may stick with the familiar gamble.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>When you avoid something because it feels uncertain, ask whether the known option is truly better.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>Finance, Work, Health, Everyday life</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>The tendency to avoid options when the probability of a good outcome is unclear, even if those options could be better than a known alternative.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>Status Quo Bias, Loss Aversion</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Ambiguity_effect</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>B050</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Identifiable Victim Effect</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Emotion</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>A single story with a face and name can move us more than numbers describing many people.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Notice when one story is pulling your attention away from the broader scale of a problem.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Media, Politics, Health, Everyday life</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>The tendency to feel and give more help in response to one identifiable person in need than to large groups described only with statistics.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>Availability Heuristic, Negativity Bias</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Identifiable_victim_effect</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>B051</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Restraint Bias</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>We predict strong self-control in advance, then struggle when the temptation is actually in front of us.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Plan for the moment of temptation, not the moment of planning.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>Health, Everyday life, Finance, Work</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>The tendency to overestimate how well we will resist temptation when the moment actually arrives.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect, Optimism Bias</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Restraint_bias</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>B052</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Reactance</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>Emotion</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Being told what to do can spark resistance, even when the advice is reasonable.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Notice when you are saying no mainly because someone told you yes — or the reverse.</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>Notice when you are saying no mainly because someone told you yes, or the reverse.</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Relationships, Work, Health, Everyday life</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>The tendency to push back when we feel our freedom is being restricted — sometimes by doing the opposite of what we are urged to do.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to push back when we feel our freedom is being restricted, sometimes by doing the opposite of what we are urged to do.</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>Status Quo Bias</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Reactance_(psychology)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>B053</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Ostrich Effect</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>Not looking can feel like relief, even though the issue remains and may grow worse unseen.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>If you are avoiding a number, email, or conversation, ask what you are afraid it will confirm.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>Finance, Health, Work, Relationships</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>The tendency to avoid looking at information that might confirm a problem we would rather not face.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias, Normalcy Bias</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Ostrich_effect</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>B054</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Zero-Sum Bias</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>Success, praise, or opportunity can feel like a fixed pie, making cooperation harder to see.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>When someone else wins, ask whether anything actually came off your plate.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>Work, Relationships, Politics, Everyday life</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>The tendency to treat a situation as if one person’s gain must mean another person’s loss, even when both could benefit.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr">
         <is>
           <t>In-group Bias</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Zero-sum_thinking</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>B055</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Moral Luck</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>Social Judgement</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>The same choice can look wise or reckless depending on results that were not fully in the person's control.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Try judging the decision separately from how lucky the outcome turned out to be.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="11" t="inlineStr">
         <is>
           <t>Work, Driving, Relationships, Everyday life</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>The tendency to judge how good or bad a decision was partly by how lucky or unlucky the outcome turned out to be.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr">
         <is>
           <t>Hindsight Bias, Fundamental Attribution Error</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Moral_luck</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>B056</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Texas Sharpshooter Fallacy</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>Patterns can be invented after the fact, making random data look meaningful.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Ask whether you are finding a pattern because you looked for it — or because you predicted it beforehand.</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Ask whether you are finding a pattern because you looked for it, or because you predicted it beforehand.</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>Work, Media, Finance, Health</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>The tendency to notice a cluster in data first, then treat that cluster as if it had been predicted — drawing the target after the shots.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>The tendency to notice a cluster in data first, then treat that cluster as if it had been predicted, drawing the target after the shots.</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>Clustering Illusion, Illusory Correlation</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Texas_sharpshooter_fallacy</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>B057</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>Overconfidence Effect</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>Self-awareness</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>Confidence can feel like proof, even when we are wrong surprisingly often.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>When you feel sure, ask what would make you only 70% sure instead of 100%.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>Work, Learning, Finance, Everyday life</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="11" t="inlineStr">
         <is>
           <t>The tendency to be more confident in our judgments than our actual accuracy usually supports.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>Dunning-Kruger Effect, Optimism Bias</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Overconfidence_effect</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>B058</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>Pro-Innovation Bias</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Work</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>Novelty can feel like progress by itself, even before evidence shows it works better.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Ask what problem the new thing solves — and what it might break.</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>Ask what problem the new thing solves, and what it might break.</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>Work, Health, Learning, Everyday life</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="11" t="inlineStr">
         <is>
           <t>The tendency to assume a new idea, tool, or innovation will help more than it will, while underestimating its limits and side effects.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias, Authority Bias</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Pro-innovation_bias</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>B059</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>Semmelweis Reflex</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>Familiar ways of doing things can feel safer than unfamiliar evidence, even when the evidence is strong.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>When a new idea feels wrong mainly because it is new, separate that feeling from whether it is actually wrong.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>Work, Health, Learning, Politics</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
         <is>
           <t>The tendency to reject new evidence or ideas mainly because they challenge established beliefs, habits, or authority.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="11" t="inlineStr">
         <is>
           <t>Belief Perseverance, Confirmation Bias</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Semmelweis_reflex</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>B060</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>Risk Compensation</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>Extra safety can lead to looser behaviour, so the overall risk may not fall as much as expected.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>When a safety measure makes you feel protected, ask whether you are relaxing in ways that bring risk back.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>Health, Driving, Everyday life, Work</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="11" t="inlineStr">
         <is>
           <t>The tendency to take greater risks when we feel protected, which can partly cancel out the safety we gained.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>Optimism Bias, Illusion of Control</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Risk_compensation</t>
         </is>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
-          <t>"I only read news that agrees with what I already believe — the rest feels untrustworthy."</t>
+          <t>"I only read news that agrees with what I already believe. The rest feels untrustworthy."</t>
         </is>
       </c>
       <c r="E2" s="19" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="K2" s="19" t="inlineStr">
         <is>
-          <t>When did you last listen to a view you disagreed with — on purpose?</t>
+          <t>When did you last listen to a view you disagreed with, on purpose?</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
         <is>
-          <t>We lean toward what fits what we already think. It feels safer and easier — but it can narrow what we're willing to hear.</t>
+          <t>We lean toward what fits what we already think. It feels safer and easier, but it can narrow what we're willing to hear.</t>
         </is>
       </c>
       <c r="M2" s="19" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>"After I bought a stock, I only followed analysts who said it would rise — and ignored warnings about debt."</t>
+          <t>"After I bought a stock, I only followed analysts who said it would rise, and ignored warnings about debt."</t>
         </is>
       </c>
       <c r="E3" s="19" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="K3" s="19" t="inlineStr">
         <is>
-          <t>After you decide something, do you look for doubts — or proof you were right?</t>
+          <t>After you decide something, do you look for doubts, or proof you were right?</t>
         </is>
       </c>
       <c r="L3" s="19" t="inlineStr">
         <is>
-          <t>Once we've committed, we want to feel we made the right call. Doubt is uncomfortable — so we often skip it.</t>
+          <t>Once we've committed, we want to feel we made the right call. Doubt is uncomfortable, so we often skip it.</t>
         </is>
       </c>
       <c r="M3" s="19" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>"My feed is full of posts I agree with — so it feels like everyone thinks the same way."</t>
+          <t>"My feed is full of posts I agree with, so it feels like everyone thinks the same way."</t>
         </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="L4" s="19" t="inlineStr">
         <is>
-          <t>We engage more with what we agree with. Platforms show us more of it — and the loop can feel like reality.</t>
+          <t>We engage more with what we agree with. Platforms show us more of it, and the loop can feel like reality.</t>
         </is>
       </c>
       <c r="M4" s="19" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>The first number we see sticks. We adjust from there — but rarely far enough.</t>
+          <t>The first number we see sticks. We adjust from there, but rarely far enough.</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>"A jacket was $300, now $150 — feels like a steal, even if $150 is still a lot."</t>
+          <t>"A jacket was $300, now $150, and it feels like a steal, even if $150 is still a lot."</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>Next 'sale' tag you see — what's the item actually worth?</t>
+          <t>Next 'sale' tag you see, what's the item actually worth?</t>
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>"In a job interview, they ask for my salary first — and that number ends up anchoring the whole negotiation."</t>
+          <t>"In a job interview, they ask for my salary first, and that number ends up anchoring the whole negotiation."</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>Early numbers are hard to let go of — even when new info suggests we should move on.</t>
+          <t>Early numbers are hard to let go of, even when new info suggests we should move on.</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>"After a few plane-crash stories in the news, flying feels terrifying — even though stats say driving is riskier."</t>
+          <t>"After a few plane-crash stories in the news, flying feels terrifying, even though stats say driving is riskier."</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>"I saw one viral post about a rare vaccine side effect — and it stuck more than the disease risks I ignored."</t>
+          <t>"I saw one viral post about a rare vaccine side effect, and it stuck more than the disease risks I ignored."</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>"After a friend's house was burgled, burglaries suddenly feel common here — even though crime has been falling."</t>
+          <t>"After a friend's house was burgled, burglaries suddenly feel common here, even though crime has been falling."</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
-          <t>Stories from people we know feel real and relevant — more than numbers on a page.</t>
+          <t>Stories from people we know feel real and relevant, more than numbers on a page.</t>
         </is>
       </c>
       <c r="M10" s="19" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>"A colleague was late to the meeting. Everyone assumed they're lazy — not knowing their car broke down."</t>
+          <t>"A colleague was late to the meeting. Everyone assumed they're lazy, not knowing their car broke down."</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>Next time someone's late — what situation might explain it?</t>
+          <t>Next time someone's late, what situation might explain it?</t>
         </is>
       </c>
       <c r="L11" s="19" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>"Someone cut me off in traffic. I thought 'what a jerk' — without wondering if they had an emergency."</t>
+          <t>"Someone cut me off in traffic. I thought 'what a jerk' without wondering if they had an emergency."</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>"A friend cancelled last minute again. I decided they're unreliable — maybe it was just a run of bad luck."</t>
+          <t>"A friend cancelled last minute again. I decided they're unreliable. Maybe it was just a run of bad luck."</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>"I passed because I'm smart — but failed last time because the questions were unfair."</t>
+          <t>"I passed because I'm smart, but failed last time because the questions were unfair."</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="K14" s="19" t="inlineStr">
         <is>
-          <t>Your last win and loss — did you explain them the same way?</t>
+          <t>Your last win and loss, did you explain them the same way?</t>
         </is>
       </c>
       <c r="L14" s="19" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>"A manager took credit when a project worked — and blamed the team when a similar one failed."</t>
+          <t>"A manager took credit when a project worked, and blamed the team when a similar one failed."</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
-          <t>When your project fails — how much do you own versus blame others?</t>
+          <t>When your project fails, how much do you own versus blame others?</t>
         </is>
       </c>
       <c r="L16" s="19" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>"I keep holding a failing stock because I've already put so much into it — hoping it'll bounce back."</t>
+          <t>"I keep holding a failing stock because I've already put so much into it, hoping it'll bounce back."</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="L17" s="19" t="inlineStr">
         <is>
-          <t>Walking away feels like admitting a mistake. Staying avoids that pain — even when it costs more.</t>
+          <t>Walking away feels like admitting a mistake. Staying avoids that pain, even when it costs more.</t>
         </is>
       </c>
       <c r="M17" s="19" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>"I've spent five years in this relationship. I can't leave now — even though I'm unhappy."</t>
+          <t>"I've spent five years in this relationship. I can't leave now, even though I'm unhappy."</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>"We keep eating a mediocre meal we already paid for — even though we could stop."</t>
+          <t>"We keep eating a mediocre meal we already paid for, even though we could stop."</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="L19" s="19" t="inlineStr">
         <is>
-          <t>We mix up 'already spent' with 'what to do next' — even when they're separate decisions.</t>
+          <t>We mix up 'already spent' with 'what to do next', even when they're separate decisions.</t>
         </is>
       </c>
       <c r="M19" s="19" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>"Nine compliments and one criticism in my review — and I obsessed over the criticism all week."</t>
+          <t>"Nine compliments and one criticism in my review, and I obsessed over the criticism all week."</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>Last feedback you got — praise or criticism stuck more?</t>
+          <t>Last feedback you got, praise or criticism stuck more?</t>
         </is>
       </c>
       <c r="L20" s="19" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>"News runs more bad stories than good ones — because negative headlines get more clicks."</t>
+          <t>"News runs more bad stories than good ones, because negative headlines get more clicks."</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>"A polished, articulate candidate seemed competent at the technical work too — without any proof."</t>
+          <t>"A polished, articulate candidate seemed competent at the technical work too, without any proof."</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>"A celebrity endorsed a health product — so fans assumed it works, because they like the celebrity."</t>
+          <t>"A celebrity endorsed a health product, so fans assumed it works, because they like the celebrity."</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>"A charismatic colleague got promoted fast — and people assumed all their ideas were good, untested ones included."</t>
+          <t>"A charismatic colleague got promoted fast, and people assumed all their ideas were good, untested ones included."</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
-          <t>A strong first impression is hard to update — even when proof is missing.</t>
+          <t>A strong first impression is hard to update, even when proof is missing.</t>
         </is>
       </c>
       <c r="M25" s="19" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>"Someone mispronounced a word in a talk — and the audience doubted whether they know the topic at all."</t>
+          <t>"Someone mispronounced a word in a talk, and the audience doubted whether they know the topic at all."</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="L27" s="19" t="inlineStr">
         <is>
-          <t>Our brain wants one consistent story — and one flaw builds a negative one fast.</t>
+          <t>Our brain wants one consistent story, and one flaw builds a negative one fast.</t>
         </is>
       </c>
       <c r="M27" s="19" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>"A public figure got one fact wrong — and viewers dismissed everything else they said, even the solid parts."</t>
+          <t>"A public figure got one fact wrong, and viewers dismissed everything else they said, even the solid parts."</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="L28" s="19" t="inlineStr">
         <is>
-          <t>One clear mistake feels like reliable evidence — even when it isn't about everything else.</t>
+          <t>One clear mistake feels like reliable evidence, even when it isn't about everything else.</t>
         </is>
       </c>
       <c r="M28" s="19" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>"Success books interview winning entrepreneurs — not the many who tried the same thing and failed."</t>
+          <t>"Success books interview winning entrepreneurs, not the many who tried the same thing and failed."</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K29" s="19" t="inlineStr">
         <is>
-          <t>Reading a success story — do you ask who tried the same and failed?</t>
+          <t>Reading a success story, do you ask who tried the same and failed?</t>
         </is>
       </c>
       <c r="L29" s="19" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>"'These five habits made CEOs successful' — with no check on failed CEOs who had the same habits."</t>
+          <t>"'These five habits made CEOs successful,' with no check on failed CEOs who had the same habits."</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>"Everyone still in the course says it's easy — but the people who struggled already dropped out."</t>
+          <t>"Everyone still in the course says it's easy, but the people who struggled already dropped out."</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="L31" s="19" t="inlineStr">
         <is>
-          <t>We hear from who's left — and forget who already walked away.</t>
+          <t>We hear from who's left, and forget who already walked away.</t>
         </is>
       </c>
       <c r="M31" s="19" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>"After a stock crashed, I said 'I knew that would happen' — though I'd bought more the week before."</t>
+          <t>"After a stock crashed, I said 'I knew that would happen', though I'd bought more the week before."</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="K32" s="19" t="inlineStr">
         <is>
-          <t>Claimed you 'knew' something — despite acting the opposite before?</t>
+          <t>Claimed you 'knew' something, despite acting the opposite before?</t>
         </is>
       </c>
       <c r="L32" s="19" t="inlineStr">
         <is>
-          <t>Once we know the ending, it feels inevitable — and our memory bends to match.</t>
+          <t>Once we know the ending, it feels inevitable, and our memory bends to match.</t>
         </is>
       </c>
       <c r="M32" s="19" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>"After the loss, I insisted 'I knew we'd lose' — though I'd predicted a win the day before."</t>
+          <t>"After the loss, I insisted 'I knew we'd lose', though I'd predicted a win the day before."</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>Could you find what you actually predicted — versus what you claim now?</t>
+          <t>Could you find what you actually predicted. Versus what you claim now?</t>
         </is>
       </c>
       <c r="L33" s="19" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>"After a project failed, the team said 'the risks were obvious from the start' — though nobody flagged them in planning."</t>
+          <t>"After a project failed, the team said 'the risks were obvious from the start', though nobody flagged them in planning."</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>"I assume most people share my political view — because everyone in my circle does."</t>
+          <t>"I assume most people share my political view, because everyone in my circle does."</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="K35" s="19" t="inlineStr">
         <is>
-          <t>How would you check if most people agree — beyond your circle?</t>
+          <t>How would you check if most people agree. Beyond your circle?</t>
         </is>
       </c>
       <c r="L35" s="19" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>"I posted a hot take online and got slammed — I'd assumed 'everyone thinks this.'"</t>
+          <t>"I posted a hot take online and got slammed. I'd assumed 'everyone thinks this.'"</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="L36" s="19" t="inlineStr">
         <is>
-          <t>Our own beliefs feel normal — so we assume others share them.</t>
+          <t>Our own beliefs feel normal, so we assume others share them.</t>
         </is>
       </c>
       <c r="M36" s="19" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>"Two people agreed in a meeting — so the manager assumed the whole team supports the policy."</t>
+          <t>"Two people agreed in a meeting, so the manager assumed the whole team supports the policy."</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="K37" s="19" t="inlineStr">
         <is>
-          <t>When few speak up — what can you really conclude about the rest?</t>
+          <t>When few speak up, what can you really conclude about the rest?</t>
         </is>
       </c>
       <c r="L37" s="19" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>"Same mistake from my department gets a pass — from another department, it's a serious problem."</t>
+          <t>"Same mistake from my department gets a pass, from another department, it's a serious problem."</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="J39" s="19" t="inlineStr">
         <is>
-          <t>Same action, different story — depending on the team.</t>
+          <t>Same action, different story, depending on the team.</t>
         </is>
       </c>
       <c r="K39" s="19" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="L39" s="19" t="inlineStr">
         <is>
-          <t>Loyalty shapes how we read ambiguous actions — we favor our side.</t>
+          <t>Loyalty shapes how we read ambiguous actions. We favor our side.</t>
         </is>
       </c>
       <c r="M39" s="19" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>"I excuse a scandal from my party — but I'm outraged by the same thing from the other side."</t>
+          <t>"I excuse a scandal from my party, but I'm outraged by the same thing from the other side."</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>"Marketing sees lots of personalities in marketing — but assumes everyone in engineering is the same."</t>
+          <t>"Marketing sees lots of personalities in marketing, but assumes everyone in engineering is the same."</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="K41" s="19" t="inlineStr">
         <is>
-          <t>Which groups do you see as diverse — and which do you lump together?</t>
+          <t>Which groups do you see as diverse, and which do you lump together?</t>
         </is>
       </c>
       <c r="L41" s="19" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>"I've never lived there — but I'm sure people from that country all think the same on this issue."</t>
+          <t>"I've never lived there, but I'm sure people from that country all think the same on this issue."</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>"A headline says 'young people today' all think one way — but we'd never describe our own generation that simply."</t>
+          <t>"A headline says 'young people today' all think one way, but we'd never describe our own generation that simply."</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>"'90% fat free' sells better than '10% fat' — same product on the label."</t>
+          <t>"'90% fat free' sells better than '10% fat', same product on the label."</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="L45" s="19" t="inlineStr">
         <is>
-          <t>Positive-sounding words trigger a warmer gut reaction — facts aside.</t>
+          <t>Positive-sounding words trigger a warmer gut reaction. Facts aside.</t>
         </is>
       </c>
       <c r="M45" s="19" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>"One side says a policy saves 200 lives. The other says it fails to save 100 — same outcome, different frame."</t>
+          <t>"One side says a policy saves 200 lives. The other says it fails to save 100, same outcome, different frame."</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>"Losing $1,000 hurts more than gaining $1,000 feels good — same amount."</t>
+          <t>"Losing $1,000 hurts more than gaining $1,000 feels good, same amount."</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="K48" s="19" t="inlineStr">
         <is>
-          <t>Last negotiation — fighting harder to keep or to gain?</t>
+          <t>Last negotiation, fighting harder to keep or to gain?</t>
         </is>
       </c>
       <c r="L48" s="19" t="inlineStr">
         <is>
-          <t>Losses are felt more intensely than equivalent gains — often about twice as much.</t>
+          <t>Losses are felt more intensely than equivalent gains, often about twice as much.</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>"I keep a gym membership I never use — canceling feels like losing something."</t>
+          <t>"I keep a gym membership I never use. Canceling feels like losing something."</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="K49" s="19" t="inlineStr">
         <is>
-          <t>Keeping something unused — value, or just fear of losing it?</t>
+          <t>Keeping something unused. Value, or just fear of losing it?</t>
         </is>
       </c>
       <c r="L49" s="19" t="inlineStr">
         <is>
-          <t>'Losing' something — even unused — can outweigh the clear case for letting go.</t>
+          <t>'Losing' something, even unused, can outweigh the clear case for letting go.</t>
         </is>
       </c>
       <c r="M49" s="19" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>"I smoke but tell myself I'm less likely to get sick than other smokers — no real reason why."</t>
+          <t>"I smoke but tell myself I'm less likely to get sick than other smokers, with no real reason why."</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>"We always estimate projects will finish early — despite a long history of running late."</t>
+          <t>"We always estimate projects will finish early, despite a long history of running late."</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="K51" s="19" t="inlineStr">
         <is>
-          <t>Does planning use real history — or just this project's best case?</t>
+          <t>Does planning use real history, or just this project's best case?</t>
         </is>
       </c>
       <c r="L51" s="19" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>"I'm not saving for retirement — I'll 'figure it out later' and assume I'll earn more than stats suggest."</t>
+          <t>"I'm not saving for retirement. I'll 'figure it out later' and assume I'll earn more than stats suggest."</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="K52" s="19" t="inlineStr">
         <is>
-          <t>Is your plan based on realistic odds — or a hoped-for best case?</t>
+          <t>Is your plan based on realistic odds, or a hoped-for best case?</t>
         </is>
       </c>
       <c r="L52" s="19" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>"I stayed in my company's default retirement plan — even though a better one needed just one form."</t>
+          <t>"I stayed in my company's default retirement plan, even though a better one needed just one form."</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>"We keep outdated software because switching feels risky — though the new system would clearly save time and money."</t>
+          <t>"We keep outdated software because switching feels risky, though the new system would clearly save time and money."</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>"I've kept my phone's default settings for years — assuming the manufacturer picked the best ones."</t>
+          <t>"I've kept my phone's default settings for years, assuming the manufacturer picked the best ones."</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="K55" s="19" t="inlineStr">
         <is>
-          <t>Default settings you've never questioned — phone, habits, anything?</t>
+          <t>Default settings you've never questioned. Phone, habits, anything?</t>
         </is>
       </c>
       <c r="L55" s="19" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>"A few articles online — and I felt more sure about my symptoms than the doctor with thousands of cases."</t>
+          <t>"A few articles online, and I felt more sure about my symptoms than the doctor with thousands of cases."</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="K58" s="19" t="inlineStr">
         <is>
-          <t>When is your own research enough — and when do you need a pro?</t>
+          <t>When is your own research enough, and when do you need a pro?</t>
         </is>
       </c>
       <c r="L58" s="19" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>"I trusted a diet tip from my doctor — even though it wasn't their area of expertise."</t>
+          <t>"I trusted a diet tip from my doctor, even though it wasn't their area of expertise."</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L59" s="19" t="inlineStr">
         <is>
-          <t>Titles and status become shortcuts for trust — instead of checking each claim.</t>
+          <t>Titles and status become shortcuts for trust, instead of checking each claim.</t>
         </is>
       </c>
       <c r="M59" s="19" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>"An actor who played a doctor on TV comments on real medicine — and viewers partly trust them because of the role."</t>
+          <t>"An actor who played a doctor on TV comments on real medicine, and viewers partly trust them because of the role."</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>"We left for the airport 'with plenty of time' — and still sprinted to the gate because packing took longer than expected."</t>
+          <t>"We left for the airport 'with plenty of time', and still sprinted to the gate because packing took longer than expected."</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>"'I'll just tidy the kitchen before guests arrive' — then the whole evening slipped because small jobs kept appearing."</t>
+          <t>"'I'll just tidy the kitchen before guests arrive', then the whole evening slipped because small jobs kept appearing."</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>"One bad week at work made me feel like I'm failing — even though the last six months went well."</t>
+          <t>"One bad week at work made me feel like I'm failing, even though the last six months went well."</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>"After one great month of saving, I felt rich — and spent more, forgetting the tighter months before."</t>
+          <t>"After one great month of saving, I felt rich, and spent more, forgetting the tighter months before."</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>"My friend cancelled once last week, so I thought they were pulling away — though they'd been reliable for years."</t>
+          <t>"My friend cancelled once last week, so I thought they were pulling away, though they'd been reliable for years."</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>"Everyone at work switched to a new app, so I did too — without checking if it actually helped me."</t>
+          <t>"Everyone at work switched to a new app, so I did too, without checking if it actually helped me."</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>If many people are doing it, it can feel validated — even before we test it ourselves.</t>
+          <t>If many people are doing it, it can feel validated, even before we test it ourselves.</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>"I bought the coat everyone was posting online — and only later wondered if I actually liked it."</t>
+          <t>"I bought the coat everyone was posting online, and only later wondered if I actually liked it."</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>"The whole group wanted the same restaurant, so I went along — even though I wanted something quieter."</t>
+          <t>"The whole group wanted the same restaurant, so I went along, even though I wanted something quieter."</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>"The new colleague seemed awkward at first — then likeable after a few lunches together."</t>
+          <t>"The new colleague seemed awkward at first, then likeable after a few lunches together."</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>"I chose the logo design we'd seen in every mock-up — not because it was best, but because it felt right."</t>
+          <t>"I chose the logo design we'd seen in every mock-up, not because it was best, but because it felt right."</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>"I wouldn't pay £80 for that mug in a shop — but I also don't want to sell mine for £80."</t>
+          <t>"I wouldn't pay £80 for that mug in a shop, but I also don't want to sell mine for £80."</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>"I priced my childhood books higher than identical copies online — because they had been on my shelf."</t>
+          <t>"I priced my childhood books higher than identical copies online, because they had been on my shelf."</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>"After three rainy weekends, I packed for sun — because it 'had to' change soon."</t>
+          <t>"After three rainy weekends, I packed for sun, because it 'had to' change soon."</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>"Our team lost twice, so I felt the next match was almost guaranteed — as if losses had to be repaid."</t>
+          <t>"Our team lost twice, so I felt the next match was almost guaranteed, as if losses had to be repaid."</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>"Two buses arrived together, so I concluded the schedule was broken — though it might have been chance."</t>
+          <t>"Two buses arrived together, so I concluded the schedule was broken, though it might have been chance."</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>"Three friends got colds the same week, so I blamed the restaurant — with no real link."</t>
+          <t>"Three friends got colds the same week, so I blamed the restaurant, with no real link."</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>"Quiet, careful, loves reading — I guessed librarian, not salesperson, without checking the odds."</t>
+          <t>"Quiet, careful, loves reading: I guessed librarian, not salesperson, without checking the odds."</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>"The polished speaker seemed like a great analyst — though their numbers did not hold up."</t>
+          <t>"The polished speaker seemed like a great analyst, though their numbers did not hold up."</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>"A startup with a sleek office felt destined to succeed — more than a scrappy one with better sales."</t>
+          <t>"A startup with a sleek office felt destined to succeed, more than a scrappy one with better sales."</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>"After one dramatic news story, I worried the problem was everywhere — though it is actually rare."</t>
+          <t>"After one dramatic news story, I worried the problem was everywhere, though it is actually rare."</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>"The test came back positive, and I panicked — forgetting how often false positives happen in screening."</t>
+          <t>"The test came back positive, and I panicked, forgetting how often false positives happen in screening."</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>"She matched the profile perfectly, so I was sure she was the right hire — though most strong profiles still fail."</t>
+          <t>"She matched the profile perfectly, so I was sure she was the right hire, though most strong profiles still fail."</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>"The dentist visit hurt most at the end, so I remembered it as painful — though most of it was fine."</t>
+          <t>"The dentist visit hurt most at the end, so I remembered it as painful, though most of it was fine."</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>"One amazing dessert at the end made me rave about a restaurant — even though the main course was average."</t>
+          <t>"One amazing dessert at the end made me rave about a restaurant, even though the main course was average."</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>"After buying the car, I kept noticing perks — and forgot the flaws I worried about in the showroom."</t>
+          <t>"After buying the car, I kept noticing perks, and forgot the flaws I worried about in the showroom."</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>Once we choose, we want to feel we chose well — so the mind edits the story.</t>
+          <t>Once we choose, we want to feel we chose well, so the mind edits the story.</t>
         </is>
       </c>
       <c r="M92" s="11" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>"I moved cities and told everyone it was perfect — though I had serious doubts the week before."</t>
+          <t>"I moved cities and told everyone it was perfect, though I had serious doubts the week before."</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>"The holiday I picked now feels like the best option — even though the other plans looked just as good."</t>
+          <t>"The holiday I picked now feels like the best option, even though the other plans looked just as good."</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>"When my team is losing, I change seats — as if where I sit could affect the score."</t>
+          <t>"When my team is losing, I change seats, as if where I sit could affect the score."</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>"I spilled coffee on my shirt and felt everyone stared — but nobody mentioned it all day."</t>
+          <t>"I spilled coffee on my shirt and felt everyone stared, but nobody mentioned it all day."</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>"I thought my bad haircut was obvious to everyone — my friends said they hadn't noticed."</t>
+          <t>"I thought my bad haircut was obvious to everyone. My friends said they hadn't noticed."</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>"I stumbled over one word in a talk and replayed it for days — the audience moved on in seconds."</t>
+          <t>"I stumbled over one word in a talk and replayed it for days. The audience moved on in seconds."</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>"I said I'd cut back on sugar — then told myself one biscuit 'doesn't count' after a hard day."</t>
+          <t>"I said I'd cut back on sugar, then told myself one biscuit 'doesn't count' after a hard day."</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>"I spent a lot on a course I rarely use — so I started saying it is 'investing in myself.'"</t>
+          <t>"I spent a lot on a course I rarely use, so I started saying it is 'investing in myself.'"</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>"People said the company was struggling, but I ignored it — we'd been stable for years."</t>
+          <t>"People said the company was struggling, but I ignored it, we'd been stable for years."</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>"I explained the form in two minutes — then watched a new starter get lost on step one."</t>
+          <t>"I explained the form in two minutes, then watched a new starter get lost on step one."</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>"My parent kept asking basic phone questions, and I got impatient — forgetting I once needed the same help."</t>
+          <t>"My parent kept asking basic phone questions, and I got impatient, forgetting I once needed the same help."</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>"The teacher said the maths was 'obvious' — but half the class was still lost on the first step."</t>
+          <t>"The teacher said the maths was 'obvious', but half the class was still lost on the first step."</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>"Every time I wear this shirt, meetings go well — so now I call it my lucky shirt."</t>
+          <t>"Every time I wear this shirt, meetings go well, so now I call it my lucky shirt."</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>"I ate sugar and got a headache — so I blamed sugar, ignoring the many sweet days with no headache."</t>
+          <t>"I ate sugar and got a headache, so I blamed sugar, ignoring the many sweet days with no headache."</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>"I'd heard the health claim so many times that it started sounding true — even though I never checked it."</t>
+          <t>"I'd heard the health claim so many times that it started sounding true, even though I never checked it."</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>"The same rumour kept appearing in my feed, so I began to believe it — no source ever checked out."</t>
+          <t>"The same rumour kept appearing in my feed, so I began to believe it, no source ever checked out."</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>"A catchy slogan from the ad campaign stuck in my head — and later felt like a fact."</t>
+          <t>"A catchy slogan from the ad campaign stuck in my head, and later felt like a fact."</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>"My colleague snapped and I called them difficult — but when I snapped, it was stress."</t>
+          <t>"My colleague snapped and I called them difficult, but when I snapped, it was stress."</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>"My friends are so confirmation-biased — I, on the other hand, just look at facts."</t>
+          <t>"My friends are so confirmation-biased. I, on the other hand, just look at facts."</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>"Everyone at the meeting was being political — except me, I was just being honest."</t>
+          <t>"Everyone at the meeting was being political. Except me, I was just being honest."</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>"I can list five biases my partner has — but struggle to name one I might share."</t>
+          <t>"I can list five biases my partner has, but struggle to name one I might share."</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>"If people were thinking clearly, they'd agree with me on this — disagreement means they're biased."</t>
+          <t>"If people were thinking clearly, they'd agree with me on this, disagreement means they're biased."</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>"The facts are right in front of us — I don't see how there are two sides to this."</t>
+          <t>"The facts are right in front of us. I don't see how there are two sides to this."</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>"After the theft, people asked what he did to make himself a target — instead of blaming the thief."</t>
+          <t>"After the theft, people asked what he did to make himself a target, instead of blaming the thief."</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>"The successful neighbour 'must have earned it' — the struggling one 'must have made bad choices.'"</t>
+          <t>"The successful neighbour 'must have earned it'. The struggling one 'must have made bad choices.'"</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>"Their short email felt deliberately cold — though they might just have been busy."</t>
+          <t>"Their short email felt deliberately cold, though they might just have been busy."</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>"Someone bumped me in the shop and I assumed they did it on purpose — they were just distracted."</t>
+          <t>"Someone bumped me in the shop and I assumed they did it on purpose. They were just distracted."</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>"Looking back, I remember doing most of the group project — my teammates remember differently."</t>
+          <t>"Looking back, I remember doing most of the group project, my teammates remember differently."</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>"I tell the story like I saved the day — though three people handled the crisis together."</t>
+          <t>"I tell the story like I saved the day, though three people handled the crisis together."</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>"I was nervous giving the toast and felt everyone could tell — they said they had no idea."</t>
+          <t>"I was nervous giving the toast and felt everyone could tell. They said they had no idea."</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>"I thought my disappointment was obvious in the meeting, so I didn't say anything — and my manager was surprised when I brought it up later."</t>
+          <t>"I thought my disappointment was obvious in the meeting, so I didn't say anything, and my manager was surprised when I brought it up later."</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>"During the argument I was sure my hurt was written all over me — my partner said I looked calm."</t>
+          <t>"During the argument I was sure my hurt was written all over me, my partner said I looked calm."</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>"I'd rather have £40 today than £60 in a month — even though I know waiting is better."</t>
+          <t>"I'd rather have £40 today than £60 in a month, even though I know waiting is better."</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>"I'll start the diet Monday — but when Monday comes, today's biscuit still wins."</t>
+          <t>"I'll start the diet Monday, but when Monday comes, today's biscuit still wins."</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>"I skipped the new treatment because the side effects weren't fully known — and stuck with the older one I understood."</t>
+          <t>"I skipped the new treatment because the side effects weren't fully known, and stuck with the older one I understood."</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>"One child's story on the news moved me to donate — statistics about thousands hadn't."</t>
+          <t>"One child's story on the news moved me to donate. Statistics about thousands hadn't."</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>"The office raised money fast for a colleague's sick parent — broader charity drives rarely do as well."</t>
+          <t>"The office raised money fast for a colleague's sick parent. Broader charity drives rarely do as well."</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>"A campaign with one patient's photo got my attention — the chart with mortality rates did not."</t>
+          <t>"A campaign with one patient's photo got my attention. The chart with mortality rates did not."</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>"I bought one biscuit for later and said I'd stop at one — I ate four once I opened the pack."</t>
+          <t>"I bought one biscuit for later and said I'd stop at one. I ate four once I opened the pack."</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>"I told myself I'd only check my phone once during dinner — and picked it up every few minutes."</t>
+          <t>"I told myself I'd only check my phone once during dinner, and picked it up every few minutes."</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>"Before the party I said I wouldn't drink much — by midnight I'd lost count."</t>
+          <t>"Before the party I said I wouldn't drink much. By midnight I'd lost count."</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>"The moment my parent told me to tidy up, I wanted to do it less — even though I had planned to."</t>
+          <t>"The moment my parent told me to tidy up, I wanted to do it less, even though I had planned to."</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>"A 'limited time only' message made me want the deal more — mostly because I hated being pushed."</t>
+          <t>"A 'limited time only' message made me want the deal more, mostly because I hated being pushed."</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>"My manager said I had to use the new form, so I dragged my feet — even though it might help."</t>
+          <t>"My manager said I had to use the new form, so I dragged my feet, even though it might help."</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>"I haven't opened my credit card app in weeks — the balance makes me tense."</t>
+          <t>"I haven't opened my credit card app in weeks. The balance makes me tense."</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>"I saw the project was slipping but avoided the status meeting — hoping it would sort itself out."</t>
+          <t>"I saw the project was slipping but avoided the status meeting, hoping it would sort itself out."</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>"If the other team gets more budget, I assume ours has to lose out — even in a growing company."</t>
+          <t>"If the other team gets more budget, I assume ours has to lose out, even in a growing company."</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>"My sibling's happy relationship somehow felt like a comment on mine — as if happiness were limited."</t>
+          <t>"My sibling's happy relationship somehow felt like a comment on mine, as if happiness were limited."</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>"Two drivers rolled through the same stop sign — one got fined, one didn't. We called one reckless and one fine."</t>
+          <t>"Two drivers rolled through the same stop sign. One got fined, one didn't. We called one reckless and one fine."</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>"A joke landed well in one room and offended in another — and we judged the teller's character differently each time."</t>
+          <t>"A joke landed well in one room and offended in another, and we judged the teller's character differently each time."</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>"After the fact, we pointed to three wins as proof of our strategy — ignoring all the misses."</t>
+          <t>"After the fact, we pointed to three wins as proof of our strategy, ignoring all the misses."</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>"All the best cafés seem to be on this street — but we only counted the good ones, not the weak ones nearby."</t>
+          <t>"All the best cafés seem to be on this street, but we only counted the good ones, not the weak ones nearby."</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>"I was 90% sure I knew the answer — and I was wrong."</t>
+          <t>"I was 90% sure I knew the answer, and I was wrong."</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="L170" s="11" t="inlineStr">
         <is>
-          <t>Confidence is a feeling, not a scorecard — but it often feels like proof.</t>
+          <t>Confidence is a feeling, not a scorecard, but it often feels like proof.</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>"We estimated the project would definitely finish early — no one built in serious delay."</t>
+          <t>"We estimated the project would definitely finish early. No one built in serious delay."</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>"I only studied the questions I was sure about — and was surprised by the ones I 'knew' I'd get right."</t>
+          <t>"I only studied the questions I was sure about, and was surprised by the ones I 'knew' I'd get right."</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>"The hospital rolled out a new app for booking — but the phones worked fine and fewer older patients could use it."</t>
+          <t>"The hospital rolled out a new app for booking, but the phones worked fine and fewer older patients could use it."</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
@@ -17245,7 +17245,7 @@
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>"The school replaced a simple paper form with a complicated portal — because 'it's time to modernise.'"</t>
+          <t>"The school replaced a simple paper form with a complicated portal, because 'it's time to modernise.'"</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>"Doctors resisted handwashing at first — the idea clashed too hard with what they already believed."</t>
+          <t>"Doctors resisted handwashing at first. The idea clashed too hard with what they already believed."</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>"The office laughed off the intern's suggestion — then adopted the same idea when a senior manager repeated it."</t>
+          <t>"The office laughed off the intern's suggestion, then adopted the same idea when a senior manager repeated it."</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>"The new handrails made the stairs feel safer — so I started texting while walking down them."</t>
+          <t>"The new handrails made the stairs feel safer, so I started texting while walking down them."</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="L181" s="11" t="inlineStr">
         <is>
-          <t>When the environment feels safer, attention can drift — and attention is its own safety layer.</t>
+          <t>When the environment feels safer, attention can drift, and attention is its own safety layer.</t>
         </is>
       </c>
       <c r="M181" s="11" t="inlineStr">
